--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>communications@royalberkshire.nhs.uk</t>
+          <t>pressoffice@berkshire.nhs.uk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -827,7 +827,11 @@
           <t>https://www.berkshirehealthcare.nhs.uk/about-us/freedom-of-information-request</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>press updated 2026-06-20: prior value communications@royalberkshire.nhs.uk belonged to Royal Berkshire (a different trust); corrected to pressoffice@berkshire.nhs.uk from the media-enquiries page</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2684,7 +2688,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.gwh.nhs.uk/contact-us/media-enquiries/</t>
+          <t>https://www.gwh.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2695,12 +2699,12 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.gwh.nhs.uk/about-us/information-governance/freedom-of-information-foi/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths.</t>
+          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths. | source URLs corrected 2026-06-20 (prior press /contact-us/media-enquiries/ 404; FOI src was a placeholder); addresses unchanged</t>
         </is>
       </c>
     </row>
@@ -2953,15 +2957,31 @@
           <t>RWR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hpft.comms@nhs.net</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.hpft.nhs.uk/contact-us/news-and-media/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>hpft.foi@nhs.net</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.hpft.nhs.uk/information-and-resources/your-information-and-privacy/foi-request-form/</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block).</t>
+          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block). | contacts added 2026-06-20 from hpft.nhs.uk (record was previously empty)</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7073,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.pah.nhs.uk/contact/media-enquiries/</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7069,7 +7089,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified.</t>
+          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified. | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7245,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget.</t>
+          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget. | 2026-06-20: Royal Marsden publishes no FOI email address (online form only)</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7420,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.torbayandsouthdevon.nhs.uk/news-and-publications/media/</t>
+          <t>https://www.torbayandsouthdevon.nhs.uk/about-us/news-and-publications/media-relations/</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7420,7 +7440,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net)</t>
+          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net) | press source URL corrected 2026-06-20 (prior URL 404); address unchanged</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -583,7 +583,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ashfordstpeters.nhs.uk/about-us/useful-contacts</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -594,12 +594,12 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ashfordstpeters.nhs.uk/about-us/useful-contacts</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site; Ashford &amp; St Peter's website returns empty body / Cloudflare-blocked to WebFetch on /, /contact-us, /freedom-of-information. Could not verify any email.</t>
+          <t>press email not found on site; FOI email not found on site; Ashford &amp; St Peter's website returns empty body / Cloudflare-blocked to WebFetch on /, /contact-us, /freedom-of-information. Could not verify any email. | press_email &amp; foi_email re-verified on site 2026-06-27 (Useful Contacts page, JS-obfuscated mailto); source_urls updated from xlsx placeholder, emails unchanged</t>
         </is>
       </c>
     </row>
@@ -1500,18 +1500,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>CRHFT.FOI@nhs.net</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>chesterfield@infreemation.co.uk</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.chesterfieldroyal.nhs.uk/about-us/contact-and-find-us/freedom-information-requests</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>FOI page not found via direct fetch; trust uses publication scheme but no public FOI email located; Chesterfield Royal FOI sub-page 404 at the obvious paths; would need direct site navigation.</t>
+          <t>FOI page not found via direct fetch; trust uses publication scheme but no public FOI email located; Chesterfield Royal FOI sub-page 404 at the obvious paths; would need direct site navigation. | foi primary updated 2026-06-27 from chesterfieldroyal.nhs.uk FOI page (only CRHFT.FOI@nhs.net shown); prior value chesterfield@infreemation.co.uk moved to foi_email_alt</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1916,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.dbth.nhs.uk/contact/communications-team/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1932,7 +1936,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address.</t>
+          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address. | press_email re-verified 2026-06-27 on Communications Team page; source_url updated from xlsx placeholder, email unchanged</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3526,12 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.lscft.nhs.uk/about-us/publications-reports-policies/freedom-information</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>FOI requests submitted via online form; no direct email provided; Lancashire &amp; South Cumbria FOI page provides postal address and online form only; no FOI email published.</t>
+          <t>FOI requests submitted via online form; no direct email provided; Lancashire &amp; South Cumbria FOI page provides postal address and online form only; no FOI email published. | foi_source_url updated 2026-06-27 to live FOI page; FOI published as postal/online-form only, email not re-confirmable on page</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5235,12 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ouh.nhs.uk/about/foi/request/</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FOI requests directed to online form, no email; subject.accessrequest@ouh.nhs.uk only for personal data/SAR; Oxford UH FOI page directs requests via online form (foienquiries.ouh.nhs.uk/start-now) and postal address; no generic FOI email published. subject.accessrequest@ouh.nhs.uk is for Subject Access only.</t>
+          <t>FOI requests directed to online form, no email; subject.accessrequest@ouh.nhs.uk only for personal data/SAR; Oxford UH FOI page directs requests via online form (foienquiries.ouh.nhs.uk/start-now) and postal address; no generic FOI email published. subject.accessrequest@ouh.nhs.uk is for Subject Access only. | foi_source_url updated 2026-06-27 to live FOI request page; FOI via online form/portal (oxford@infreemation.co.uk), email unchanged</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -4034,7 +4034,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/contact/</t>
+          <t>https://www.mtw.nhs.uk/news/media-enquiries-and-contacts/</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4045,10 +4045,14 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/contact/</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>https://www.mtw.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-07-04: source URLs refreshed (old /contact/ now 404); FOI mtw-tr.foiadmin@nhs.net confirmed live, press email unchanged (media page blocks automated fetch).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4896,7 +4900,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.northamptongeneral.nhs.uk/News/Communications-team.aspx</t>
+          <t>https://www.northamptongeneral.nhs.uk/Services/Our-Non-Clinical-Services-and-Departments/Communications.aspx</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4916,7 +4920,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>FOI email retrieved via Wayback snapshot of publication scheme page</t>
+          <t>FOI email retrieved via Wayback snapshot of publication scheme page 2026-07-04: press source URL refreshed (old News/Communications-team.aspx 404); ngh-tr.communications@nhs.net re-confirmed.</t>
         </is>
       </c>
     </row>
@@ -7018,12 +7022,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.thh.nhs.uk/about-us/freedom-of-information</t>
+          <t>https://thh.nhs.uk/freedom-of-information/</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026.</t>
+          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026. 2026-07-04: FOI source URL refreshed (old /about-us/ page 404); still online-form only (thh.disclosure-log.co.uk), no email published.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -863,7 +863,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.bhamcommunity.nhs.uk/freedom-of-information/</t>
+          <t>https://www.bhamcommunity.nhs.uk/foi/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ruh.nhs.uk/foi/overview_obtain_information.asp?menu_id=1</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7564,7 +7564,7 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.uhs.nhs.uk/about-the-trust/privacy/requesting-information-about-university-hospital-southampton</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2664,12 +2664,12 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.gosh.nhs.uk/about-us/freedom-information-act-0/make-foi-request/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>GOSH FOI page not located (homepage and search returned no FOI link; /about-us/freedom-of-information/ returns 404). Likely available only via direct contact with information governance; GOSH FOI sub-pages 404 across multiple tested paths; press-office page links to FOI but target unreachable.</t>
+          <t>GOSH FOI page not located (homepage and search returned no FOI link; /about-us/freedom-of-information/ returns 404). Likely available only via direct contact with information governance; GOSH FOI sub-pages 404 across multiple tested paths; press-office page links to FOI but target unreachable. | foi_source_url updated 2026-07-18 to live FOI page (foiteam@gosh.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.hampshirehospitals.nhs.uk/our-services/az-departments-and-specialties/media-enquiries</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>press email not found on contact pages; Hampshire Hospitals: no press email surfaced (contact page returned 403).</t>
+          <t>press email not found on contact pages; Hampshire Hospitals: no press email surfaced (contact page returned 403). | press_source_url updated 2026-07-18 to live media-enquiries page (communications@hhft.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
         </is>
       </c>
     </row>
@@ -3928,12 +3928,12 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.liverpoolwomens.nhs.uk/media/1795/foi-publication-scheme.pdf</t>
+          <t>https://www.uhliverpool.nhs.uk/freedom-information-requests-lwh</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme</t>
+          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme | foi_source_url updated 2026-07-18 to live UHL group FOI page (FOI@lwh.nhs.uk confirmed); prior liverpoolwomens.nhs.uk PDF now redirects to the group site. Group submission inbox FOIRequests@liverpoolft.nhs.uk also seen (not adopted as primary)</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2083,12 +2083,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.ekhuft.nhs.uk/patients-and-visitors/about-us/freedom-of-information/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration.</t>
+          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration. FOI source URL resolved 2026-07-30 to /patients-and-visitors/about-us/freedom-of-information/ (site migration complete); ekh-tr.FOI@nhs.net confirmed on page, address unchanged.</t>
         </is>
       </c>
     </row>
@@ -7055,10 +7055,14 @@
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://www.newcastle-hospitals.nhs.uk/help/foi/</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Newcastle press email inferred from Bing cross-reference (Cloudflare-encoded on page); FOI page directs requests via online form, no email.</t>
+          <t>Newcastle press email inferred from Bing cross-reference (Cloudflare-encoded on page); FOI page directs requests via online form, no email. FOI source URL recorded 2026-07-30: /help/foi/ re-checked and still publishes no FOI mailbox - requests go through an on-page web form only, so foi_email stays null.</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7128,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.qehkl.nhs.uk/news-and-events/media-enquiries/</t>
+          <t>https://www.qehkl.nhs.uk/about-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7144,7 +7148,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>FOI uses combined data protection / FOI inbox</t>
+          <t>FOI uses combined data protection / FOI inbox press source URL updated 2026-07-30: /news-and-events/media-enquiries/ now 404s, page moved to /about-us/media-enquiries/; media.enquiries@qehkl.nhs.uk confirmed there, address unchanged. Note the FOI page designates foi@qehkl.nhs.uk (currently held in _alt) while dpa@ is the data-protection inbox.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2533,14 +2533,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>geh@infreemation.co.uk</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>freedom.ofinformation@geh.nhs.uk</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>foi@geh.nhs.uk</t>
-        </is>
-      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>https://www.geh.nhs.uk/about-us/governance/freedom-information</t>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>in progress [2026-08-01] foi_email primary updated 2026-08-01 from https://www.geh.nhs.uk/about-us/governance/freedom-information — the page now routes requests to the Infreemation portal address geh@infreemation.co.uk and keeps freedom.ofinformation@geh.nhs.uk only for complaints/appeals, so that prior primary moved to _alt; the previous _alt foi@geh.nhs.uk is no longer published.</t>
         </is>
       </c>
     </row>
@@ -3754,10 +3754,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>lhnt.foi.lchs@nhs.net</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>agcsu.foi.lchs@nhs.net</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information</t>
@@ -3765,7 +3769,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FOI handled via shared CSU inbox</t>
+          <t>FOI handled via shared CSU inbox [2026-08-01] foi_email primary updated 2026-08-01 from https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information; prior value agcsu.foi.lchs@nhs.net moved to _alt.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -1953,10 +1953,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>dch.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>communications@dchft.nhs.uk</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>https://www.dchft.nhs.uk/about-us/contact-us/</t>
@@ -1979,7 +1983,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FOI inbox is shared with Dorset HealthCare (dhc prefix)</t>
+          <t>FOI inbox is shared with Dorset HealthCare (dhc prefix); press primary updated 2026-08-08 from https://www.dchft.nhs.uk/about-us/contact-us/ (page lists dch.communications@nhs.net as the media/communications contact); prior value communications@dchft.nhs.uk moved to press_email_alt</t>
         </is>
       </c>
     </row>
@@ -4461,14 +4465,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>eec.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>ccs.communications@nhs.net</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Communications@nchc.nhs.uk</t>
-        </is>
-      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
@@ -4476,14 +4480,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>eec.accesstoinfo@nhs.net</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>ccs.accesstoinfo@nhs.net</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>FreedomOfInformationProvider@nchc.nhs.uk</t>
-        </is>
-      </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
@@ -4491,7 +4495,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV)</t>
+          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV); press and FOI primaries updated 2026-08-08 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us — the merged trust now publishes eec.communications@nhs.net (media) and eec.accesstoinfo@nhs.net (FOI); prior values ccs.communications@nhs.net and ccs.accesstoinfo@nhs.net moved to the _alt fields, displacing the legacy Norfolk Community addresses Communications@nchc.nhs.uk and FreedomOfInformationProvider@nchc.nhs.uk, which are recorded here so they are not lost</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -1109,7 +1109,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.bradfordhospitals.nhs.uk/media-enquiries/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No press/comms email found on news-and-media page; switchboard 01274 542200 the only contact route; No dedicated press email surfaced on news/media or contact-us pages.</t>
+          <t>No press/comms email found on news-and-media page; switchboard 01274 542200 the only contact route; No dedicated press email surfaced on news/media or contact-us pages. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.bradfordhospitals.nhs.uk/media-enquiries/].</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.eastamb.nhs.uk/media-team</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EEAST: no press/media email visible on contact, newsroom, in-the-news, or about-us pages; site is Next.js app with limited static contact info; East of England Ambulance contact page lists feedback@ and charity@ only; no dedicated press email published.</t>
+          <t>EEAST: no press/media email visible on contact, newsroom, in-the-news, or about-us pages; site is Next.js app with limited static contact info; East of England Ambulance contact page lists feedback@ and charity@ only; no dedicated press email published. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.eastamb.nhs.uk/media-team].</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.stockport.nhs.uk/pressoffice/</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Contact page lists no media or FOI emails; FOI page not yet checked; Stockport FOI email decoded from Cloudflare cfemail. Contact-us page 404; no press email surfaced.</t>
+          <t>Contact page lists no media or FOI emails; FOI page not yet checked; Stockport FOI email decoded from Cloudflare cfemail. Contact-us page 404; no press email surfaced. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.stockport.nhs.uk/pressoffice/].</t>
         </is>
       </c>
     </row>
@@ -6806,33 +6806,37 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
+          <t>nlft.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
           <t>media@tavi-port.nhs.uk</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>communications@tavi-port.nhs.uk</t>
-        </is>
-      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://tavistockandportman.nhs.uk/contact-us/media/</t>
+          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
+          <t>nlft.freedom.information@nhs.net</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
           <t>foi@tavi-port.nhs.uk</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://tavistockandportman.nhs.uk/about-us/freedom-information/</t>
+          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Trust merged into North London FT April 2026; archived site; Note: Tavistock &amp; Portman merged into North London NHS FT on 1 April 2026 - site archived.</t>
+          <t>Trust merged into North London FT April 2026; archived site; Note: Tavistock &amp; Portman merged into North London NHS FT on 1 April 2026 - site archived. 2026-08-15: tavistockandportman.nhs.uk now 301-redirects to northlondonmentalhealth.nhs.uk (North London NHS Foundation Trust); both prior source URLs are dead. press + foi primaries updated from [https://www.northlondonmentalhealth.nhs.uk/contact-us]; prior values moved to _alt (displaced prior press _alt was communications@tavi-port.nhs.uk).</t>
         </is>
       </c>
     </row>
@@ -8255,12 +8259,12 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.whittington.nhs.uk/default.asp?c=1631</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>FOI email not located; Whittington FOI sub-pages (default.asp ?c= numeric IDs) all 404 in tests.</t>
+          <t>FOI email not located; Whittington FOI sub-pages (default.asp ?c= numeric IDs) all 404 in tests. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.whittington.nhs.uk/default.asp?c=1631].</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8287,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8294,12 +8298,12 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.wchc.nhs.uk/about/freedom-information/act/</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>no listed emails on either page; phone-only contact; Wirral Community: contact page lists media phone numbers but no email; FOI page lists no email; sub-paths 404.</t>
+          <t>no listed emails on either page; phone-only contact; Wirral Community: contact page lists media phone numbers but no email; FOI page lists no email; sub-paths 404. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/]. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/freedom-information/act/].</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -5342,11 +5342,7 @@
           <t>pho-tr.communications@nhs.net</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>communications@porthosp.nhs.uk</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>https://www.porthosp.nhs.uk/about-us/contact-us</t>
@@ -5369,7 +5365,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>2026-08-18: press_email pho-tr.communications@nhs.net re-verified against the trust's own contact-us page. Stale alt communications@porthosp.nhs.uk removed - reported as wrong. Note: Isle of Wight NHS Trust (R1F) legitimately shares this same comms inbox.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -5478,7 +5478,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page.</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. Trust asks media to route all enquiries via the press office rather than contacting staff directly.</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page. Press address is listed there as 'Website Enquiries / Media / Press', so it is not media-only.</t>
         </is>
       </c>
     </row>
@@ -8442,12 +8442,12 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/freedom-of-information-requests.aspx</t>
+          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/make-a-freedom-of-information-request.aspx</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. foi_source_url repointed - the old freedom-of-information-requests.aspx now 404s. Press office page also lists three named comms staff (John Burnett, comms and engagement manager; Amanda Millichip and Fiona Gurney, comms officers) on 01432 372928.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -425,7 +425,7 @@
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
@@ -2129,7 +2129,11 @@
           <t>https://elht.nhs.uk/contact-us</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-08-22: contact page could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); communications@elht.nhs.uk and foi@elht.nhs.uk both corroborated against the 20 June 2026 Wayback snapshot, addresses left unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2712,7 +2716,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths. | source URLs corrected 2026-06-20 (prior press /contact-us/media-enquiries/ 404; FOI src was a placeholder); addresses unchanged</t>
+          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths. | source URLs corrected 2026-06-20 (prior press /contact-us/media-enquiries/ 404; FOI src was a placeholder); addresses unchanged | 2026-08-22: /contact/ publishes only gwh.webmaster@nhs.net - no press address on the page, so gwh.comms@nhs.net is retained unverified this run; gwh.foi@nhs.net re-confirmed on the FOI page.</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2993,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block). | contacts added 2026-06-20 from hpft.nhs.uk (record was previously empty)</t>
+          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block). | contacts added 2026-06-20 from hpft.nhs.uk (record was previously empty) | 2026-08-22: both addresses confirmed via headless browser (hpft.comms@nhs.net on /contact-us/news-and-media/, hpft.foi@nhs.net on the FOI request form page); the pages still 403 plain fetches, so the earlier 'not found on site' note is superseded.</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3973,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>londamb.foi@nhs.net?subject=enquiry%20from%20london%20ambulance%20service%20website</t>
+          <t>londamb.foi@nhs.net</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3982,7 +3986,11 @@
           <t>https://www.londonambulance.nhs.uk/talking-with-us/freedom-of-information/classes-of-information/</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-22: foi_email cleaned to londamb.foi@nhs.net - the stored value carried a '?subject=...' mailto querystring that is not part of the address; address itself re-confirmed against published LAS FOI responses. Press address re-confirmed by decoding the cfemail token on the press page.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6032,7 +6040,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>FOI uses third-party Infreemation portal</t>
+          <t>FOI uses third-party Infreemation portal | 2026-08-22: contact and FOI pages could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); shropcom.FOIR@infreemation.co.uk corroborated against a 2026 Wayback snapshot, addresses left unchanged.</t>
         </is>
       </c>
     </row>
@@ -6135,10 +6143,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
+          <t>scas.oncallmedia@nhs.net</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
           <t>oncallmedia@scas.nhs.uk</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>https://www.scas.nhs.uk/contact-us/contact-the-media-team/</t>
@@ -6146,16 +6158,24 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
+          <t>scas.foi2@nhs.net</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
           <t>foi@scas.nhs.uk</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>https://www.scas.nhs.uk/contact-us/</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>primary updated 2026-08-22 from https://www.scas.nhs.uk/contact-us/contact-the-media-team/ and https://www.scas.nhs.uk/contact-us/; prior values moved to _alt (press oncallmedia@scas.nhs.uk, foi foi@scas.nhs.uk) - the trust now publishes nhs.net team mailboxes on both pages</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7101,15 +7121,19 @@
           <t>paht.FOI@nhs.net</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>FOI@pah.nhs.uk</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.pah.nhs.uk/foi/request/</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified. | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged</t>
+          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified. | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged | 2026-08-22: foi_source_url repointed from the spreadsheet placeholder to the live /foi/request/ page (online form only, no address published there); FOI@pah.nhs.uk recorded as _alt from the trust's own FOI guidance. Press address paht.communications@nhs.net re-confirmed by decoding the cfemail token on the media-enquiries page.</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7289,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget. | 2026-06-20: Royal Marsden publishes no FOI email address (online form only)</t>
+          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget. | 2026-06-20: Royal Marsden publishes no FOI email address (online form only) | 2026-08-22: pressteam@rmh.nhs.uk re-confirmed; FOI page still publishes no address (online form only), so foi_email stays null.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7484,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net) | press source URL corrected 2026-06-20 (prior URL 404); address unchanged</t>
+          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net) | press source URL corrected 2026-06-20 (prior URL 404); address unchanged | 2026-08-22: media-relations page is contact-form only with no address published, so the reconstructed press address is retained unverified; tsdft.foirequests@nhs.net re-confirmed.</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7648,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site</t>
+          <t>press email not found on site; FOI email not found on site | 2026-08-22: both addresses now confirmed on the trust's own pages (communications@uhb.nhs.uk on /get-in-touch/media-enquiries/, Foi@uhb.nhs.uk on /get-in-touch/make-a-freedom-of-information-request/) - the earlier 'not found on site' note is superseded.</t>
         </is>
       </c>
     </row>
@@ -8442,12 +8466,12 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/make-a-freedom-of-information-request.aspx</t>
+          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. foi_source_url repointed - the old freedom-of-information-requests.aspx now 404s. Press office page also lists three named comms staff (John Burnett, comms and engagement manager; Amanda Millichip and Fiona Gurney, comms officers) on 01432 372928.</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. foi_source_url repointed - the old freedom-of-information-requests.aspx now 404s. Press office page also lists three named comms staff (John Burnett, comms and engagement manager; Amanda Millichip and Fiona Gurney, comms officers) on 01432 372928. | 2026-08-22: foi_source_url repointed again - make-a-freedom-of-information-request.aspx now 404s; Freedom.Information@wvt.nhs.uk is published on the parent /about-us/information-requests/ page. Press address re-confirmed on the press office page.</t>
         </is>
       </c>
     </row>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1132,194 +1132,190 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bridgewater Community Healthcare NHS Foundation Trust</t>
+          <t>Buckinghamshire Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RY2</t>
+          <t>RXQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ncm.media@nhs.net</t>
+          <t>bht.communications@nhs.net</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://northcheshireandmersey.nhs.uk/contact-us/</t>
+          <t>https://www.buckshealthcare.nhs.uk/get-in-touch/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ncm.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>foi@bridgewater.nhs.uk</t>
-        </is>
-      </c>
+          <t>bht.bhinfo@nhs.net</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Bridgewater merged into North Cheshire &amp; Mersey FT; shared inbox</t>
-        </is>
-      </c>
+          <t>https://www.buckshealthcare.nhs.uk/our-organisation/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Buckinghamshire Healthcare NHS Trust</t>
+          <t>Calderdale and Huddersfield NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RXQ</t>
+          <t>RWY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bht.communications@nhs.net</t>
+          <t>amy.campbell@cht.nhs.uk</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.buckshealthcare.nhs.uk/get-in-touch/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>bht.bhinfo@nhs.net</t>
+          <t>FOI@cht.nhs.uk</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.buckshealthcare.nhs.uk/our-organisation/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>https://www.cht.nhs.uk/publications/freedom-of-information-foi/about-freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Calderdale &amp; Huddersfield: contact-us page lists no emails; FOI sub-pages 404; no public-facing FOI email visible.; FOI email confirmed via Google site search May 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calderdale and Huddersfield NHS Foundation Trust</t>
+          <t>Cambridge University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RWY</t>
+          <t>RGT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>amy.campbell@cht.nhs.uk</t>
+          <t>cuh.press@nhs.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.cuh.nhs.uk/contact-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FOI@cht.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>cuh.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>foi.contact@addenbrookes.nhs.uk</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.cht.nhs.uk/publications/freedom-of-information-foi/about-freedom-of-information/</t>
+          <t>https://www.cuh.nhs.uk/about-us/freedom-information/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Calderdale &amp; Huddersfield: contact-us page lists no emails; FOI sub-pages 404; no public-facing FOI email visible.; FOI email confirmed via Google site search May 2026.</t>
+          <t>CUH FOI page returned 404; FOI process exists but specific email not confirmed; CUH contact page lists only phone numbers; FOI sub-pages 404 across multiple paths.; FOI primary updated 2026-05-16 from https://www.cuh.nhs.uk/about-us/freedom-information/; prior value moved to _alt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cambridge University Hospitals NHS Foundation Trust</t>
+          <t>Cambridgeshire and Peterborough NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RGT</t>
+          <t>RT1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cuh.press@nhs.net</t>
+          <t>communications@cpft.nhs.uk</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.cuh.nhs.uk/contact-us/media-enquiries/</t>
+          <t>https://www.cpft.nhs.uk/press-and-media</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>cuh.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>foi.contact@addenbrookes.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@cpft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.cuh.nhs.uk/about-us/freedom-information/</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CUH FOI page returned 404; FOI process exists but specific email not confirmed; CUH contact page lists only phone numbers; FOI sub-pages 404 across multiple paths.; FOI primary updated 2026-05-16 from https://www.cuh.nhs.uk/about-us/freedom-information/; prior value moved to _alt</t>
-        </is>
-      </c>
+          <t>https://www.cpft.nhs.uk/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cambridgeshire and Peterborough NHS Foundation Trust</t>
+          <t>Central London Community Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RT1</t>
+          <t>RYX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>communications@cpft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>clcht.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>clch.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.cpft.nhs.uk/press-and-media</t>
+          <t>https://www.clch.nhs.uk/about-us/contact-us</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>foi@cpft.nhs.uk</t>
+          <t>foi.request@nhs.net</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.cpft.nhs.uk/freedom-of-information</t>
+          <t>https://www.clch.nhs.uk/about-us/contact-us</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1327,38 +1323,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Central London Community Healthcare NHS Trust</t>
+          <t>Central and North West London NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RYX</t>
+          <t>RV3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>clcht.comms@nhs.net</t>
+          <t>cnwl.communications@nhs.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>clch.communications@nhs.net</t>
+          <t>communications.cnwl@nhs.net</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.clch.nhs.uk/about-us/contact-us</t>
+          <t>https://www.cnwl.nhs.uk/news/press-office</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>foi.request@nhs.net</t>
+          <t>freedomofinformation.cnwl@nhs.net</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.clch.nhs.uk/about-us/contact-us</t>
+          <t>https://www.cnwl.nhs.uk/about/freedom-information-foi</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1366,38 +1362,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Central and North West London NHS Foundation Trust</t>
+          <t>Chelsea and Westminster Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RV3</t>
+          <t>RQM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cnwl.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>communications.cnwl@nhs.net</t>
-        </is>
-      </c>
+          <t>chelwest.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.cnwl.nhs.uk/news/press-office</t>
+          <t>https://www.chelwest.nhs.uk/about-us/news/press-office</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>freedomofinformation.cnwl@nhs.net</t>
+          <t>chelwest.foi@nhs.net</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.cnwl.nhs.uk/about/freedom-information-foi</t>
+          <t>https://www.chelwest.nhs.uk/about-us/organisation/our-way-of-working/foi/freedom-of-information</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1405,155 +1397,155 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chelsea and Westminster Hospital NHS Foundation Trust</t>
+          <t>Cheshire and Wirral Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RQM</t>
+          <t>RXA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>chelwest.comms@nhs.net</t>
+          <t>jodie.denrico@cwp.nhs.uk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.chelwest.nhs.uk/about-us/news/press-office</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>chelwest.foi@nhs.net</t>
+          <t>cwp.foi@nhs.net</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.chelwest.nhs.uk/about-us/organisation/our-way-of-working/foi/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cheshire and Wirral Partnership website Cloudflare bot-protected; could not retrieve contact pages; Cheshire &amp; Wirral Partnership: all contact and FOI pages returned 403 to WebFetch (server-side bot block).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cheshire and Wirral Partnership NHS Foundation Trust</t>
+          <t>Chesterfield Royal Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RXA</t>
+          <t>RFS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jodie.denrico@cwp.nhs.uk</t>
+          <t>crhft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.chesterfieldroyal.nhs.uk/about-us/contact-and-find-us/media-enquires</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>cwp.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>CRHFT.FOI@nhs.net</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>chesterfield@infreemation.co.uk</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.chesterfieldroyal.nhs.uk/about-us/contact-and-find-us/freedom-information-requests</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cheshire and Wirral Partnership website Cloudflare bot-protected; could not retrieve contact pages; Cheshire &amp; Wirral Partnership: all contact and FOI pages returned 403 to WebFetch (server-side bot block).</t>
+          <t>FOI page not found via direct fetch; trust uses publication scheme but no public FOI email located; Chesterfield Royal FOI sub-page 404 at the obvious paths; would need direct site navigation. | foi primary updated 2026-06-27 from chesterfieldroyal.nhs.uk FOI page (only CRHFT.FOI@nhs.net shown); prior value chesterfield@infreemation.co.uk moved to foi_email_alt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chesterfield Royal Hospital NHS Foundation Trust</t>
+          <t>Cornwall Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RJ8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>crhft.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>cftcommunications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>cpn-tr.Enquiries@nhs.net</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.chesterfieldroyal.nhs.uk/about-us/contact-and-find-us/media-enquires</t>
+          <t>https://www.cornwallft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CRHFT.FOI@nhs.net</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>chesterfield@infreemation.co.uk</t>
-        </is>
-      </c>
+          <t>cpn-tr.freedomofinformation@nhs.net</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.chesterfieldroyal.nhs.uk/about-us/contact-and-find-us/freedom-information-requests</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>FOI page not found via direct fetch; trust uses publication scheme but no public FOI email located; Chesterfield Royal FOI sub-page 404 at the obvious paths; would need direct site navigation. | foi primary updated 2026-06-27 from chesterfieldroyal.nhs.uk FOI page (only CRHFT.FOI@nhs.net shown); prior value chesterfield@infreemation.co.uk moved to foi_email_alt</t>
-        </is>
-      </c>
+          <t>https://www.cornwallft.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cornwall Partnership NHS Foundation Trust</t>
+          <t>Countess of Chester Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RJ8</t>
+          <t>RJR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>cftcommunications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>cpn-tr.Enquiries@nhs.net</t>
-        </is>
-      </c>
+          <t>countess.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.cornwallft.nhs.uk/contact-us/</t>
+          <t>https://www.coch.nhs.uk/contact-us/press-office.aspx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>cpn-tr.freedomofinformation@nhs.net</t>
+          <t>foi.enquiries@nhs.net</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.cornwallft.nhs.uk/freedom-of-information/</t>
+          <t>https://www.coch.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1561,34 +1553,34 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Countess of Chester Hospital NHS Foundation Trust</t>
+          <t>County Durham and Darlington NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RJR</t>
+          <t>RXP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>countess.communications@nhs.net</t>
+          <t>cdda-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.coch.nhs.uk/contact-us/press-office.aspx</t>
+          <t>https://www.cddft.nhs.uk/about-us/media-centre</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>foi.enquiries@nhs.net</t>
+          <t>cdda-tr.cddftfoi@nhs.net</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.coch.nhs.uk/contact-us/</t>
+          <t>https://www.cddft.nhs.uk/about-us/corporate-information/freedom-information</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1596,264 +1588,268 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>County Durham and Darlington NHS Foundation Trust</t>
+          <t>Coventry and Warwickshire Partnership NHS Trust</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RXP</t>
+          <t>RYG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>cdda-tr.communications@nhs.net</t>
+          <t>media@covwarkpt.nhs.uk</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.cddft.nhs.uk/about-us/media-centre</t>
+          <t>https://www.covwarkpt.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>cdda-tr.cddftfoi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>mlcsusars@nhs.net</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>freedomofinformation@covwarkpt.nhs.uk</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.cddft.nhs.uk/about-us/corporate-information/freedom-information</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>https://www.covwarkpt.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FOI handled by NHS Midlands and Lancashire CSU shared service</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Coventry and Warwickshire Partnership NHS Trust</t>
+          <t>Croydon Health Services NHS Trust</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RYG</t>
+          <t>RJ6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>media@covwarkpt.nhs.uk</t>
+          <t>chs.comms@nhs.net</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.covwarkpt.nhs.uk/contact-us</t>
+          <t>https://www.croydonhealthservices.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>mlcsusars@nhs.net</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>freedomofinformation@covwarkpt.nhs.uk</t>
-        </is>
-      </c>
+          <t>ch-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.covwarkpt.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>FOI handled by NHS Midlands and Lancashire CSU shared service</t>
-        </is>
-      </c>
+          <t>https://www.croydonhealthservices.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Croydon Health Services NHS Trust</t>
+          <t>Cumbria, Northumberland, Tyne and Wear NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RJ6</t>
+          <t>RX4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>chs.comms@nhs.net</t>
+          <t>communications@cntw.nhs.uk</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.croydonhealthservices.nhs.uk/contact-us</t>
+          <t>https://www.cntw.nhs.uk/contact/press/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ch-tr.foi@nhs.net</t>
+          <t>foi@cntw.nhs.uk</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.croydonhealthservices.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>https://www.cntw.nhs.uk/foi/request/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Cloudflare email-protection decoded</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cumbria, Northumberland, Tyne and Wear NHS Foundation Trust</t>
+          <t>Dartford and Gravesham NHS Trust</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RX4</t>
+          <t>RN7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>communications@cntw.nhs.uk</t>
+          <t>dgn-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/contact/press/</t>
+          <t>https://www.dgt.nhs.uk/contact-us/communicationpress-darent-valley-hospital</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>foi@cntw.nhs.uk</t>
+          <t>dgn-tr.freedomofinformation@nhs.net</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/foi/request/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cloudflare email-protection decoded</t>
+          <t>FOI page provided online form/post but no direct email; Dartford &amp; Gravesham FOI page lists only postal address and online form; no email published.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dartford and Gravesham NHS Trust</t>
+          <t>Derbyshire Community Health Services NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RN7</t>
+          <t>RY8</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dgn-tr.communications@nhs.net</t>
+          <t>DCHST.communications@nhs.net</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.dgt.nhs.uk/contact-us/communicationpress-darent-valley-hospital</t>
+          <t>https://dchs.nhs.uk/contact-and-find-us</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>dgn-tr.freedomofinformation@nhs.net</t>
+          <t>DCHST.FreedomofInformation@nhs.net</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://dchs.nhs.uk/about-us/freedom-information</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>FOI page provided online form/post but no direct email; Dartford &amp; Gravesham FOI page lists only postal address and online form; no email published.</t>
+          <t>contact pages return 404; investigating</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Derbyshire Community Health Services NHS Foundation Trust</t>
+          <t>Derbyshire Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RY8</t>
+          <t>RXM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DCHST.communications@nhs.net</t>
+          <t>dhcft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://dchs.nhs.uk/contact-and-find-us</t>
+          <t>https://www.derbyshirehealthcareft.nhs.uk/contact-us/media-enquiries</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DCHST.FreedomofInformation@nhs.net</t>
+          <t>dhcft.foienquiries@nhs.net</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://dchs.nhs.uk/about-us/freedom-information</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>contact pages return 404; investigating</t>
-        </is>
-      </c>
+          <t>https://www.derbyshirehealthcareft.nhs.uk/contact-us/freedom-information-requests</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Derbyshire Healthcare NHS Foundation Trust</t>
+          <t>Devon Partnership NHS Trust</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RXM</t>
+          <t>RWV</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dhcft.communications@nhs.net</t>
+          <t>dpn-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.derbyshirehealthcareft.nhs.uk/contact-us/media-enquiries</t>
+          <t>https://www.dpt.nhs.uk/get-in-touch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>dhcft.foienquiries@nhs.net</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>dpt.ig@nhs.net</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>dpt.saferinformation@nhs.net</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.derbyshirehealthcareft.nhs.uk/contact-us/freedom-information-requests</t>
+          <t>https://www.dpt.nhs.uk/get-in-touch</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -1861,163 +1857,159 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Devon Partnership NHS Trust</t>
+          <t>Doncaster and Bassetlaw Teaching Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RWV</t>
+          <t>RP5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dpn-tr.communications@nhs.net</t>
+          <t>Adam.Tingle@nhs.net</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.dpt.nhs.uk/get-in-touch</t>
+          <t>https://www.dbth.nhs.uk/contact/communications-team/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>dpt.ig@nhs.net</t>
+          <t>d.wraith@nhs.net</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>dpt.saferinformation@nhs.net</t>
+          <t>dbth.foi@nhs.net</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.dpt.nhs.uk/get-in-touch</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>https://www.dbth.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address. | press_email re-verified 2026-06-27 on Communications Team page; source_url updated from xlsx placeholder, email unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Doncaster and Bassetlaw Teaching Hospitals NHS Foundation Trust</t>
+          <t>Dorset County Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RP5</t>
+          <t>RBD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Adam.Tingle@nhs.net</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>dch.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>communications@dchft.nhs.uk</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.dbth.nhs.uk/contact/communications-team/</t>
+          <t>https://www.dchft.nhs.uk/about-us/contact-us/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>d.wraith@nhs.net</t>
+          <t>dhc.dch.foi.enquiries@nhs.net</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>dbth.foi@nhs.net</t>
+          <t>FOI@dchft.nhs.uk</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.dbth.nhs.uk/about-us/freedom-of-information/</t>
+          <t>https://www.dchft.nhs.uk/about-us/contact-us/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address. | press_email re-verified 2026-06-27 on Communications Team page; source_url updated from xlsx placeholder, email unchanged</t>
+          <t>FOI inbox is shared with Dorset HealthCare (dhc prefix); press primary updated 2026-08-08 from https://www.dchft.nhs.uk/about-us/contact-us/ (page lists dch.communications@nhs.net as the media/communications contact); prior value communications@dchft.nhs.uk moved to press_email_alt</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dorset County Hospital NHS Foundation Trust</t>
+          <t>Dorset Healthcare University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RBD</t>
+          <t>RDY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dch.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>communications@dchft.nhs.uk</t>
-        </is>
-      </c>
+          <t>dhc.communications.team@nhs.net</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.dchft.nhs.uk/about-us/contact-us/</t>
+          <t>https://www.dorsethealthcare.nhs.uk/about-us/contact-us</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>dhc.dch.foi.enquiries@nhs.net</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>FOI@dchft.nhs.uk</t>
-        </is>
-      </c>
+          <t>dhc.foi.enquiries@nhs.net</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.dchft.nhs.uk/about-us/contact-us/</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>FOI inbox is shared with Dorset HealthCare (dhc prefix); press primary updated 2026-08-08 from https://www.dchft.nhs.uk/about-us/contact-us/ (page lists dch.communications@nhs.net as the media/communications contact); prior value communications@dchft.nhs.uk moved to press_email_alt</t>
-        </is>
-      </c>
+          <t>https://www.dorsethealthcare.nhs.uk/about-us/contact-us</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dorset Healthcare University NHS Foundation Trust</t>
+          <t>East Cheshire NHS Trust</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RDY</t>
+          <t>RJN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dhc.communications.team@nhs.net</t>
+          <t>ecntstaff.comms@nhs.net</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.dorsethealthcare.nhs.uk/about-us/contact-us</t>
+          <t>https://trust.eastcheshire.nhs.uk/corporate-services/communications-and-engagement</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>dhc.foi.enquiries@nhs.net</t>
+          <t>ecn-tr.foirequests@nhs.net</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.dorsethealthcare.nhs.uk/about-us/contact-us</t>
+          <t>https://trust.eastcheshire.nhs.uk/freedom-information</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2025,147 +2017,147 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>East Cheshire NHS Trust</t>
+          <t>East Kent Hospitals University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RJN</t>
+          <t>RVV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ecntstaff.comms@nhs.net</t>
+          <t>ekh-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://trust.eastcheshire.nhs.uk/corporate-services/communications-and-engagement</t>
+          <t>https://www.ekhuft.nhs.uk/contact-us/press-office</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ecn-tr.foirequests@nhs.net</t>
+          <t>ekh-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://trust.eastcheshire.nhs.uk/freedom-information</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>https://www.ekhuft.nhs.uk/patients-and-visitors/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration. FOI source URL resolved 2026-07-30 to /patients-and-visitors/about-us/freedom-of-information/ (site migration complete); ekh-tr.FOI@nhs.net confirmed on page, address unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>East Kent Hospitals University NHS Foundation Trust</t>
+          <t>East Lancashire Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RVV</t>
+          <t>RXR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ekh-tr.communications@nhs.net</t>
+          <t>communications@elht.nhs.uk</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.ekhuft.nhs.uk/contact-us/press-office</t>
+          <t>https://elht.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ekh-tr.foi@nhs.net</t>
+          <t>foi@elht.nhs.uk</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.ekhuft.nhs.uk/patients-and-visitors/about-us/freedom-of-information/</t>
+          <t>https://elht.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FOI page not located; ekhuft.nhs.uk/foi redirects to archive that 404s; East Kent Hospitals FOI page redirects to www-archive.ekhuft.nhs.uk and 404s; site mid-migration. FOI source URL resolved 2026-07-30 to /patients-and-visitors/about-us/freedom-of-information/ (site migration complete); ekh-tr.FOI@nhs.net confirmed on page, address unchanged.</t>
+          <t>2026-08-22: contact page could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); communications@elht.nhs.uk and foi@elht.nhs.uk both corroborated against the 20 June 2026 Wayback snapshot, addresses left unchanged.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>East Lancashire Hospitals NHS Trust</t>
+          <t>East London NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RXR</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>communications@elht.nhs.uk</t>
+          <t>elft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://elht.nhs.uk/contact-us</t>
+          <t>https://www.elft.nhs.uk/contact-us/press-enquiries</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>foi@elht.nhs.uk</t>
+          <t>elft.foi@nhs.net</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://elht.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-08-22: contact page could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); communications@elht.nhs.uk and foi@elht.nhs.uk both corroborated against the 20 June 2026 Wayback snapshot, addresses left unchanged.</t>
-        </is>
-      </c>
+          <t>https://www.elft.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>East London NHS Foundation Trust</t>
+          <t>East Midlands Ambulance Service NHS Trust</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>RX9</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>elft.communications@nhs.net</t>
+          <t>emascommunications@emas.nhs.uk</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.elft.nhs.uk/contact-us/press-enquiries</t>
+          <t>https://www.emas.nhs.uk/news/media-enquiries/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>elft.foi@nhs.net</t>
+          <t>foi.foi@emas.nhs.uk</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.elft.nhs.uk/contact-us</t>
+          <t>https://www.emas.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2173,34 +2165,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>East Midlands Ambulance Service NHS Trust</t>
+          <t>East Suffolk and North Essex NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RX9</t>
+          <t>RDE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>emascommunications@emas.nhs.uk</t>
+          <t>communications@esneft.nhs.uk</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.emas.nhs.uk/news/media-enquiries/</t>
+          <t>https://www.esneft.nhs.uk/contact-us/communications-team/</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>foi.foi@emas.nhs.uk</t>
+          <t>foi@esneft.nhs.uk</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.emas.nhs.uk/contact-us/</t>
+          <t>https://www.esneft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2208,717 +2200,717 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>East Suffolk and North Essex NHS Foundation Trust</t>
+          <t>East Sussex Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RDE</t>
+          <t>RXC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>communications@esneft.nhs.uk</t>
+          <t>esht.communications@nhs.net</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.esneft.nhs.uk/contact-us/communications-team/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>foi@esneft.nhs.uk</t>
+          <t>esh-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.esneft.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>https://www.esht.nhs.uk/about-us/contact-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>press uses web form, no listed email; East Sussex Healthcare media enquiries page closed connection on fetch; no press email retrieved.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>East Sussex Healthcare NHS Trust</t>
+          <t>East and North Hertfordshire NHS Trust</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RXC</t>
+          <t>RWH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>esht.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>pressoffice@enherts-tr.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>communications.enh-tr@nhs.net</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.enherts-tr.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>esh-tr.foi@nhs.net</t>
+          <t>foi.enh-tr@nhs.net</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.esht.nhs.uk/about-us/contact-us/freedom-of-information/</t>
+          <t>https://www.enherts-tr.nhs.uk/foi/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>press uses web form, no listed email; East Sussex Healthcare media enquiries page closed connection on fetch; no press email retrieved.</t>
+          <t>Both emails obscured by Cloudflare email-protection on the pages | press primary updated 2026-05-29 from [https://www.enherts-tr.nhs.uk/contact/]; prior value communications.enh-tr@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>East and North Hertfordshire NHS Trust</t>
+          <t>East of England Ambulance Service NHS Trust</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RWH</t>
+          <t>RYC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>pressoffice@enherts-tr.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>communications.enh-tr@nhs.net</t>
-        </is>
-      </c>
+          <t>media@eastamb.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.enherts-tr.nhs.uk/contact/</t>
+          <t>https://www.eastamb.nhs.uk/media-team</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>foi.enh-tr@nhs.net</t>
+          <t>FOI@eastamb.nhs.uk</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.enherts-tr.nhs.uk/foi/</t>
+          <t>https://www.eastamb.nhs.uk/about-us/freedom-of-information</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Both emails obscured by Cloudflare email-protection on the pages | press primary updated 2026-05-29 from [https://www.enherts-tr.nhs.uk/contact/]; prior value communications.enh-tr@nhs.net moved to _alt</t>
+          <t>EEAST: no press/media email visible on contact, newsroom, in-the-news, or about-us pages; site is Next.js app with limited static contact info; East of England Ambulance contact page lists feedback@ and charity@ only; no dedicated press email published. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.eastamb.nhs.uk/media-team].</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>East of England Ambulance Service NHS Trust</t>
+          <t>Epsom and St Helier University Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RYC</t>
+          <t>RVR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>media@eastamb.nhs.uk</t>
+          <t>gesh.comms@stgeorges.nhs.uk</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.eastamb.nhs.uk/media-team</t>
+          <t>https://www.epsom-sthelier.nhs.uk/media-enquiries</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FOI@eastamb.nhs.uk</t>
+          <t>esth.foi@nhs.net</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.eastamb.nhs.uk/about-us/freedom-of-information</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>EEAST: no press/media email visible on contact, newsroom, in-the-news, or about-us pages; site is Next.js app with limited static contact info; East of England Ambulance contact page lists feedback@ and charity@ only; no dedicated press email published. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.eastamb.nhs.uk/media-team].</t>
+          <t>GESH group press inbox shared with St George's; FOI directs to online form, no email; Epsom &amp; St Helier FOI page provides only postal address and online form; no email.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Epsom and St Helier University Hospitals NHS Trust</t>
+          <t>Essex Partnership University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RVR</t>
+          <t>R1L</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gesh.comms@stgeorges.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>communications@eput.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>epunft.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.epsom-sthelier.nhs.uk/media-enquiries</t>
+          <t>https://www.eput.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>esth.foi@nhs.net</t>
+          <t>epunft.FOI@nhs.net</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.eput.nhs.uk/about/freedom-of-information/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>GESH group press inbox shared with St George's; FOI directs to online form, no email; Epsom &amp; St Helier FOI page provides only postal address and online form; no email.</t>
+          <t>FOI email obfuscated as [email protected] on website; could not extract; EPUT FOI email decoded from Cloudflare cfemail attribute (epunft = Essex Partnership University NHS Foundation Trust).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Essex Partnership University NHS Foundation Trust</t>
+          <t>Frimley Health NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R1L</t>
+          <t>RDU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>communications@eput.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>epunft.communications@nhs.net</t>
-        </is>
-      </c>
+          <t>fhft.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.eput.nhs.uk/contact/</t>
+          <t>https://www.fhft.nhs.uk/news</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>epunft.FOI@nhs.net</t>
+          <t>fhft.foi@nhs.net</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.eput.nhs.uk/about/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>FOI email obfuscated as [email protected] on website; could not extract; EPUT FOI email decoded from Cloudflare cfemail attribute (epunft = Essex Partnership University NHS Foundation Trust).</t>
-        </is>
-      </c>
+          <t>https://www.fhft.nhs.uk/about-us/corporate-information-and-publications/freedom-information-foi</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Frimley Health NHS Foundation Trust</t>
+          <t>Gateshead Health NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RDU</t>
+          <t>RR7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fhft.communications@nhs.net</t>
+          <t>ghnt.comms@nhs.net</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.fhft.nhs.uk/news</t>
+          <t>https://www.gatesheadhealth.nhs.uk/press/</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>fhft.foi@nhs.net</t>
+          <t>ghnt.foi.enquiries@nhs.net</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.fhft.nhs.uk/about-us/corporate-information-and-publications/freedom-information-foi</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>https://www.gatesheadhealth.nhs.uk/foi/</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Decoded from CloudFlare cfemail data attributes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gateshead Health NHS Foundation Trust</t>
+          <t>George Eliot Hospital NHS Trust</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RR7</t>
+          <t>RLT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ghnt.comms@nhs.net</t>
+          <t>communications@geh.nhs.uk</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.gatesheadhealth.nhs.uk/press/</t>
+          <t>https://www.geh.nhs.uk/contact-us/media-enquiries</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ghnt.foi.enquiries@nhs.net</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>geh@infreemation.co.uk</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>freedom.ofinformation@geh.nhs.uk</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.gatesheadhealth.nhs.uk/foi/</t>
+          <t>https://www.geh.nhs.uk/about-us/governance/freedom-information</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Decoded from CloudFlare cfemail data attributes</t>
+          <t>in progress [2026-08-01] foi_email primary updated 2026-08-01 from https://www.geh.nhs.uk/about-us/governance/freedom-information — the page now routes requests to the Infreemation portal address geh@infreemation.co.uk and keeps freedom.ofinformation@geh.nhs.uk only for complaints/appeals, so that prior primary moved to _alt; the previous _alt foi@geh.nhs.uk is no longer published.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>George Eliot Hospital NHS Trust</t>
+          <t>Gloucestershire Health and Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RLT</t>
+          <t>RTQ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>communications@geh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>ghccomms@ghc.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2gnft.comms@nhs.net</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.geh.nhs.uk/contact-us/media-enquiries</t>
+          <t>https://www.ghc.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>geh@infreemation.co.uk</t>
+          <t>foi@ghc.nhs.uk</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>freedom.ofinformation@geh.nhs.uk</t>
+          <t>FreedomofInformation@ghc.nhs.uk</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.geh.nhs.uk/about-us/governance/freedom-information</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>in progress [2026-08-01] foi_email primary updated 2026-08-01 from https://www.geh.nhs.uk/about-us/governance/freedom-information — the page now routes requests to the Infreemation portal address geh@infreemation.co.uk and keeps freedom.ofinformation@geh.nhs.uk only for complaints/appeals, so that prior primary moved to _alt; the previous _alt foi@geh.nhs.uk is no longer published.</t>
-        </is>
-      </c>
+          <t>https://www.ghc.nhs.uk/who-we-are/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gloucestershire Health and Care NHS Foundation Trust</t>
+          <t>Gloucestershire Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTQ</t>
+          <t>RTE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ghccomms@ghc.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2gnft.comms@nhs.net</t>
-        </is>
-      </c>
+          <t>ghn-tr.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.ghc.nhs.uk/contact-us/</t>
+          <t>https://www.gloshospitals.nhs.uk/about-us/news-media/media-enquiries/</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>foi@ghc.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>FreedomofInformation@ghc.nhs.uk</t>
-        </is>
-      </c>
+          <t>ghn-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.ghc.nhs.uk/who-we-are/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>https://www.gloshospitals.nhs.uk/about-us/our-trust/freedom-information/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>FOI page not located on attempted URLs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gloucestershire Hospitals NHS Foundation Trust</t>
+          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RTE</t>
+          <t>RP4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ghn-tr.comms@nhs.net</t>
+          <t>media@gosh.nhs.uk</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.gloshospitals.nhs.uk/about-us/news-media/media-enquiries/</t>
+          <t>https://www.gosh.nhs.uk/press-office/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ghn-tr.foi@nhs.net</t>
+          <t>foiteam@gosh.nhs.uk</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.gloshospitals.nhs.uk/about-us/our-trust/freedom-information/</t>
+          <t>https://www.gosh.nhs.uk/about-us/freedom-information-act-0/make-foi-request/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>FOI page not located on attempted URLs</t>
+          <t>GOSH FOI page not located (homepage and search returned no FOI link; /about-us/freedom-of-information/ returns 404). Likely available only via direct contact with information governance; GOSH FOI sub-pages 404 across multiple tested paths; press-office page links to FOI but target unreachable. | foi_source_url updated 2026-07-18 to live FOI page (foiteam@gosh.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Great Ormond Street Hospital for Children NHS Foundation Trust</t>
+          <t>Great Western Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RP4</t>
+          <t>RN3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>media@gosh.nhs.uk</t>
+          <t>gwh.comms@nhs.net</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.gosh.nhs.uk/press-office/</t>
+          <t>https://www.gwh.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>foiteam@gosh.nhs.uk</t>
+          <t>gwh.foi@nhs.net</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.gosh.nhs.uk/about-us/freedom-information-act-0/make-foi-request/</t>
+          <t>https://www.gwh.nhs.uk/about-us/information-governance/freedom-of-information-foi/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>GOSH FOI page not located (homepage and search returned no FOI link; /about-us/freedom-of-information/ returns 404). Likely available only via direct contact with information governance; GOSH FOI sub-pages 404 across multiple tested paths; press-office page links to FOI but target unreachable. | foi_source_url updated 2026-07-18 to live FOI page (foiteam@gosh.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
+          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths. | source URLs corrected 2026-06-20 (prior press /contact-us/media-enquiries/ 404; FOI src was a placeholder); addresses unchanged | 2026-08-22: /contact/ publishes only gwh.webmaster@nhs.net - no press address on the page, so gwh.comms@nhs.net is retained unverified this run; gwh.foi@nhs.net re-confirmed on the FOI page.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Great Western Hospitals NHS Foundation Trust</t>
+          <t>Greater Manchester Mental Health NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RN3</t>
+          <t>RXV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gwh.comms@nhs.net</t>
+          <t>communications@gmmh.nhs.uk</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.gwh.nhs.uk/contact/</t>
+          <t>https://www.gmmh.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>gwh.foi@nhs.net</t>
+          <t>foi@gmmh.nhs.uk</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.gwh.nhs.uk/about-us/information-governance/freedom-of-information-foi/</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>FOI page not located; Great Western Hospitals FOI sub-pages 404 across all common paths. | source URLs corrected 2026-06-20 (prior press /contact-us/media-enquiries/ 404; FOI src was a placeholder); addresses unchanged | 2026-08-22: /contact/ publishes only gwh.webmaster@nhs.net - no press address on the page, so gwh.comms@nhs.net is retained unverified this run; gwh.foi@nhs.net re-confirmed on the FOI page.</t>
-        </is>
-      </c>
+          <t>https://www.gmmh.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Greater Manchester Mental Health NHS Foundation Trust</t>
+          <t>Guy's and St Thomas' NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RXV</t>
+          <t>RJ1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>communications@gmmh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>gstt.press@nhs.net</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>press@gstt.nhs.uk</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.gmmh.nhs.uk/contact-us</t>
+          <t>https://www.guysandstthomas.nhs.uk/news/contacts-media-enquiries</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>foi@gmmh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>gstt.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>foi@gstt.nhs.uk</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.gmmh.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>https://www.guysandstthomas.nhs.uk/about-us/freedom-information</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>FOI email obfuscated by Cloudflare on FOI page; not confirmed; FOI email decoded from Cloudflare cfemail attribute on FOI page.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Guy's and St Thomas' NHS Foundation Trust</t>
+          <t>Hampshire Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RJ1</t>
+          <t>RN5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>gstt.press@nhs.net</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>press@gstt.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications@hhft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.guysandstthomas.nhs.uk/news/contacts-media-enquiries</t>
+          <t>https://www.hampshirehospitals.nhs.uk/our-services/az-departments-and-specialties/media-enquiries</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>gstt.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>foi@gstt.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@hhft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.guysandstthomas.nhs.uk/about-us/freedom-information</t>
+          <t>https://www.hampshirehospitals.nhs.uk/about-us/freedom-information</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>FOI email obfuscated by Cloudflare on FOI page; not confirmed; FOI email decoded from Cloudflare cfemail attribute on FOI page.</t>
+          <t>press email not found on contact pages; Hampshire Hospitals: no press email surfaced (contact page returned 403). | press_source_url updated 2026-07-18 to live media-enquiries page (communications@hhft.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hampshire Hospitals NHS Foundation Trust</t>
+          <t>Harrogate and District NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RN5</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>communications@hhft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>communications@hdft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>hdft.hello@nhs.net</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.hampshirehospitals.nhs.uk/our-services/az-departments-and-specialties/media-enquiries</t>
+          <t>https://www.hdft.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>foi@hhft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>foi@hdft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>hdft.foi@nhs.net</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.hampshirehospitals.nhs.uk/about-us/freedom-information</t>
+          <t>https://www.hdft.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>press email not found on contact pages; Hampshire Hospitals: no press email surfaced (contact page returned 403). | press_source_url updated 2026-07-18 to live media-enquiries page (communications@hhft.nhs.uk confirmed on page); prior value was an internal spreadsheet placeholder</t>
+          <t>Both press and FOI emails on hdft.nhs.uk are obfuscated as [email protected]; confirmed contact phone numbers (press 01423 557470) but emails not extractable</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Harrogate and District NHS Foundation Trust</t>
+          <t>Herefordshire and Worcestershire Health and Care NHS Trust</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RCD</t>
+          <t>R1A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>communications@hdft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>hdft.hello@nhs.net</t>
-        </is>
-      </c>
+          <t>whcnhs.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.hdft.nhs.uk/contact/</t>
+          <t>https://www.hacw.nhs.uk/media-enquiries-</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>foi@hdft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>hdft.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>WHCNHS.FOIrequest@nhs.net</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.hdft.nhs.uk/contact/</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Both press and FOI emails on hdft.nhs.uk are obfuscated as [email protected]; confirmed contact phone numbers (press 01423 557470) but emails not extractable</t>
-        </is>
-      </c>
+          <t>https://www.hacw.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Herefordshire and Worcestershire Health and Care NHS Trust</t>
+          <t>Hertfordshire Community NHS Trust</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R1A</t>
+          <t>RY4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>whcnhs.communications@nhs.net</t>
+          <t>hct.communications@nhs.net</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.hacw.nhs.uk/media-enquiries-</t>
+          <t>https://www.hct.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WHCNHS.FOIrequest@nhs.net</t>
+          <t>hct.foi@nhs.net</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.hacw.nhs.uk/freedom-of-information/</t>
+          <t>https://www.hct.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2926,280 +2918,268 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hertfordshire Community NHS Trust</t>
+          <t>Hertfordshire Partnership University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RY4</t>
+          <t>RWR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>hct.communications@nhs.net</t>
+          <t>hpft.comms@nhs.net</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.hct.nhs.uk/contact-us/</t>
+          <t>https://www.hpft.nhs.uk/contact-us/news-and-media/</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>hct.foi@nhs.net</t>
+          <t>hpft.foi@nhs.net</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.hct.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>https://www.hpft.nhs.uk/information-and-resources/your-information-and-privacy/foi-request-form/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block). | contacts added 2026-06-20 from hpft.nhs.uk (record was previously empty) | 2026-08-22: both addresses confirmed via headless browser (hpft.comms@nhs.net on /contact-us/news-and-media/, hpft.foi@nhs.net on the FOI request form page); the pages still 403 plain fetches, so the earlier 'not found on site' note is superseded.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hertfordshire Partnership University NHS Foundation Trust</t>
+          <t>Homerton Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RWR</t>
+          <t>RQX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hpft.comms@nhs.net</t>
+          <t>mark.purcell@nhs.net</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.hpft.nhs.uk/contact-us/news-and-media/</t>
+          <t>https://www.homerton.nhs.uk/press-office</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>hpft.foi@nhs.net</t>
+          <t>huh-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.hpft.nhs.uk/information-and-resources/your-information-and-privacy/foi-request-form/</t>
+          <t>https://www.homerton.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site; Hertfordshire Partnership University: contact-us and FOI pages returned 403 to WebFetch (bot block). | contacts added 2026-06-20 from hpft.nhs.uk (record was previously empty) | 2026-08-22: both addresses confirmed via headless browser (hpft.comms@nhs.net on /contact-us/news-and-media/, hpft.foi@nhs.net on the FOI request form page); the pages still 403 plain fetches, so the earlier 'not found on site' note is superseded.</t>
+          <t>Homerton press contact is named individual (Mark Purcell) rather than team inbox</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Homerton Healthcare NHS Foundation Trust</t>
+          <t>Hull University Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RQX</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mark.purcell@nhs.net</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>nlg-tr.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>hyp-tr.comms@nhs.net</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.homerton.nhs.uk/press-office</t>
+          <t>https://www.hull.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>huh-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>hyp-tr.huthfoi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>hyp-tr.foi@nhs.net</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.homerton.nhs.uk/contact-us</t>
+          <t>https://www.hull.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Homerton press contact is named individual (Mark Purcell) rather than team inbox</t>
+          <t>hey.nhs.uk redirects to hull.nhs.uk; FOI page hey.nhs.uk/about-us/freedom-of-information redirects to nlg.nhs.uk/foi (NLAG sister trust)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hounslow and Richmond Community Healthcare NHS Trust</t>
+          <t>Humber Teaching NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RY9</t>
+          <t>RV9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>krft.comms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>hrch.communications@nhs.net</t>
-        </is>
-      </c>
+          <t>HNF-TR.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.kingstonandrichmond.nhs.uk/about-us/news/media-enquiries</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>krft.foienquiries@nhs.net</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>hrch.freedomofinformation@nhs.net</t>
-        </is>
-      </c>
+          <t>https://www.humber.nhs.uk/news/media-and-communications/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.kingstonandrichmond.nhs.uk/patients-and-families/patient-records-and-privacy/freedom-information-and-access-records</t>
+          <t>https://www.humber.nhs.uk/about/freedom-of-information-and-publication-scheme/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Hounslow &amp; Richmond merged into Kingston &amp; Richmond NHS Group; site redirects to kingstonandrichmond.nhs.uk</t>
+          <t>FOI directs to online form, no direct email listed; Humber FOI page directs requests via online form; no email published.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hull University Teaching Hospitals NHS Trust</t>
+          <t>Imperial College Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>RYJ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nlg-tr.comms@nhs.net</t>
+          <t>imperial.press.office@nhs.net</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>hyp-tr.comms@nhs.net</t>
+          <t>cara.barrett@nhs.net</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.hull.nhs.uk/contact/</t>
+          <t>https://www.imperial.nhs.uk/contact-and-find-us/press-office</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>hyp-tr.huthfoi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>hyp-tr.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>imperial.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.hull.nhs.uk/contact/</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>hey.nhs.uk redirects to hull.nhs.uk; FOI page hey.nhs.uk/about-us/freedom-of-information redirects to nlg.nhs.uk/foi (NLAG sister trust)</t>
-        </is>
-      </c>
+          <t>https://www.imperial.nhs.uk/about-us/foi/freedom-of-information-requests</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Humber Teaching NHS Foundation Trust</t>
+          <t>Isle of Wight NHS Trust</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RV9</t>
+          <t>R1F</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HNF-TR.communications@nhs.net</t>
+          <t>pho-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.humber.nhs.uk/news/media-and-communications/</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>https://www.iow.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>iownt.freedomofinformation@nhs.net</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.humber.nhs.uk/about/freedom-of-information-and-publication-scheme/</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>FOI directs to online form, no direct email listed; Humber FOI page directs requests via online form; no email published.</t>
-        </is>
-      </c>
+          <t>https://www.iow.nhs.uk/about-us/requesting-information</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Imperial College Healthcare NHS Trust</t>
+          <t>James Paget University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RYJ</t>
+          <t>RGP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>imperial.press.office@nhs.net</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>cara.barrett@nhs.net</t>
-        </is>
-      </c>
+          <t>communications@jpaget.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.imperial.nhs.uk/contact-and-find-us/press-office</t>
+          <t>https://www.jpaget.nhs.uk/departments/communications-media/</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>imperial.foi@nhs.net</t>
+          <t>FOI@jpaget.nhs.uk</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.imperial.nhs.uk/about-us/foi/freedom-of-information-requests</t>
+          <t>https://www.jpaget.nhs.uk/about-us/freedom-of-information/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3207,34 +3187,34 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Isle of Wight NHS Trust</t>
+          <t>Kent Community Health NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R1F</t>
+          <t>RYY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pho-tr.communications@nhs.net</t>
+          <t>kchft.comms@nhs.net</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.iow.nhs.uk/contact-us</t>
+          <t>https://www.kentcht.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>iownt.freedomofinformation@nhs.net</t>
+          <t>kcht.foi@nhs.net</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.iow.nhs.uk/about-us/requesting-information</t>
+          <t>https://www.kentcht.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3242,69 +3222,77 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>James Paget University Hospitals NHS Foundation Trust</t>
+          <t>Kent and Medway NHS and Social Care Partnership Trust</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RGP</t>
+          <t>RXY</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>communications@jpaget.nhs.uk</t>
+          <t>comms.kentandmedway@nhs.net</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.jpaget.nhs.uk/departments/communications-media/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FOI@jpaget.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>kmmh.infoaccess@nhs.net</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>kmpt.infoaccess@nhs.net</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.jpaget.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>http://www.kentmedwaymentalhealth.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>trust rebranded to Kent Medway Mental Health; press via web form only; KMPT contact page provides media enquiries form only; no published press email.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kent Community Health NHS Foundation Trust</t>
+          <t>Kettering General Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RYY</t>
+          <t>RNQ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>kchft.comms@nhs.net</t>
+          <t>kgh-tr.Comms@nhs.net</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.kentcht.nhs.uk/contact/</t>
+          <t>https://www.kgh.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>kcht.foi@nhs.net</t>
+          <t>kgh-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.kentcht.nhs.uk/contact/</t>
+          <t>https://www.kgh.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3312,190 +3300,202 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kent and Medway NHS and Social Care Partnership Trust</t>
+          <t>King's College Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RXY</t>
+          <t>RJZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>comms.kentandmedway@nhs.net</t>
+          <t>kch-tr.mediateam@nhs.net</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.kch.nhs.uk/news/press-media-and-filming/contacting-the-media-team</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>kmmh.infoaccess@nhs.net</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>kmpt.infoaccess@nhs.net</t>
-        </is>
-      </c>
+          <t>kch-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://www.kentmedwaymentalhealth.nhs.uk/about-us/freedom-of-information/</t>
+          <t>https://www.kch.nhs.uk/about/corporate-information/freedom-of-information/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>trust rebranded to Kent Medway Mental Health; press via web form only; KMPT contact page provides media enquiries form only; no published press email.</t>
+          <t>FOI email obfuscated by Cloudflare; postal/online form available; FOI email decoded from Cloudflare cfemail attribute.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kettering General Hospital NHS Foundation Trust</t>
+          <t>Kingston and Richmond NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RNQ</t>
+          <t>RAX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kgh-tr.Comms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>krft.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>hrch.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.kgh.nhs.uk/contact-us</t>
+          <t>https://www.kingstonandrichmond.nhs.uk/about-us/news/media-enquiries</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>kgh-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>krft.foienquiries@nhs.net</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>hrch.freedomofinformation@nhs.net</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.kgh.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>https://www.kingstonandrichmond.nhs.uk/patients-and-families/patient-records-and-privacy/freedom-information-and-access-records</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-08-22 ODS merge reconciliation: row RY9 (Hounslow and Richmond Community Healthcare) retired and folded in; merged 1 Nov 2024 to form Kingston and Richmond NHS FT. Legacy HRCH inboxes kept as _alt.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>King's College Hospital NHS Foundation Trust</t>
+          <t>Lancashire Teaching Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RJZ</t>
+          <t>RXN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>kch-tr.mediateam@nhs.net</t>
+          <t>communication@lthtr.nhs.uk</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.kch.nhs.uk/news/press-media-and-filming/contacting-the-media-team</t>
+          <t>https://www.lancsteachinghospitals.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>kch-tr.foi@nhs.net</t>
+          <t>freedomofinformation@lthtr.nhs.uk</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.kch.nhs.uk/about/corporate-information/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>FOI email obfuscated by Cloudflare; postal/online form available; FOI email decoded from Cloudflare cfemail attribute.</t>
-        </is>
-      </c>
+          <t>https://www.lancsteachinghospitals.nhs.uk/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kingston Hospital NHS Foundation Trust</t>
+          <t>Lancashire and South Cumbria NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RAX</t>
+          <t>RW5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>krft.comms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>communications@lscft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>communications@lancashirecare.nhs.uk</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.kingstonandrichmond.nhs.uk/about-us/news/media-enquiries</t>
+          <t>https://www.lscft.nhs.uk/contact-us/press-and-media</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>krft.foienquiries@nhs.net</t>
+          <t>FOIRequests@lancashirecare.nhs.uk</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.kingstonandrichmond.nhs.uk/patients-and-families/patient-records-and-privacy/freedom-information-and-access-records</t>
+          <t>https://www.lscft.nhs.uk/about-us/publications-reports-policies/freedom-information</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Trust now Kingston and Richmond NHS FT (merger). FOI email not surfaced on contact page</t>
+          <t>FOI requests submitted via online form; no direct email provided; Lancashire &amp; South Cumbria FOI page provides postal address and online form only; no FOI email published. | foi_source_url updated 2026-06-27 to live FOI page; FOI published as postal/online-form only, email not re-confirmable on page</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lancashire Teaching Hospitals NHS Foundation Trust</t>
+          <t>Leeds Community Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RXN</t>
+          <t>RY6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>communication@lthtr.nhs.uk</t>
+          <t>lch.comms@nhs.net</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.lancsteachinghospitals.nhs.uk/contact-us</t>
+          <t>https://leedscommunityhealthcare.nhs.uk/contact-us/press-and-media-enquiries/</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>freedomofinformation@lthtr.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>ig.lch@nhs.net</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>foi.lch@nhs.net</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.lancsteachinghospitals.nhs.uk/freedom-of-information</t>
+          <t>https://leedscommunityhealthcare.nhs.uk/about-us/access-to-information/data-requests-your-privacy/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -3503,81 +3503,73 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lancashire and South Cumbria NHS Foundation Trust</t>
+          <t>Leeds Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RW5</t>
+          <t>RR8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>communications@lscft.nhs.uk</t>
+          <t>leedsth-tr.researchcomms@nhs.net</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>communications@lancashirecare.nhs.uk</t>
+          <t>communications.lth@nhs.net</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.lscft.nhs.uk/contact-us/press-and-media</t>
+          <t>https://www.leedsth.nhs.uk/research/contact-us/</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FOIRequests@lancashirecare.nhs.uk</t>
+          <t>leedsth-tr.informationgovernance@nhs.net</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.lscft.nhs.uk/about-us/publications-reports-policies/freedom-information</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>FOI requests submitted via online form; no direct email provided; Lancashire &amp; South Cumbria FOI page provides postal address and online form only; no FOI email published. | foi_source_url updated 2026-06-27 to live FOI page; FOI published as postal/online-form only, email not re-confirmable on page</t>
-        </is>
-      </c>
+          <t>https://www.leedsth.nhs.uk/about/information-governance/subject-access-requests/</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leeds Community Healthcare NHS Trust</t>
+          <t>Leeds and York Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RY6</t>
+          <t>RGD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>lch.comms@nhs.net</t>
+          <t>communications.lypft@nhs.net</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leedscommunityhealthcare.nhs.uk/contact-us/press-and-media-enquiries/</t>
+          <t>https://www.leedsandyorkpft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ig.lch@nhs.net</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>foi.lch@nhs.net</t>
-        </is>
-      </c>
+          <t>foi.lypft@nhs.net</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://leedscommunityhealthcare.nhs.uk/about-us/access-to-information/data-requests-your-privacy/</t>
+          <t>https://www.leedsandyorkpft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3585,38 +3577,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Leeds Teaching Hospitals NHS Trust</t>
+          <t>Leicestershire Partnership NHS Trust</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RR8</t>
+          <t>RT5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>leedsth-tr.researchcomms@nhs.net</t>
+          <t>lpt.communications@nhs.net</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>communications.lth@nhs.net</t>
+          <t>kamy.basra@leicspart.nhs.uk</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.leedsth.nhs.uk/research/contact-us/</t>
+          <t>https://www.leicspart.nhs.uk/contact/comms/</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>leedsth-tr.informationgovernance@nhs.net</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>lpt.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>FOIrequests@leicspart.nhs.uk</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.leedsth.nhs.uk/about/information-governance/subject-access-requests/</t>
+          <t>https://www.leicspart.nhs.uk/about/freedom-of-information-requests/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -3624,34 +3620,34 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Leeds and York Partnership NHS Foundation Trust</t>
+          <t>Lewisham and Greenwich NHS Trust</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RGD</t>
+          <t>RJ2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>communications.lypft@nhs.net</t>
+          <t>lg.communications@nhs.net</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.leedsandyorkpft.nhs.uk/contact-us/</t>
+          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>foi.lypft@nhs.net</t>
+          <t>foi.lg@nhs.net</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.leedsandyorkpft.nhs.uk/contact-us/</t>
+          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -3659,77 +3655,89 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Leicestershire Partnership NHS Trust</t>
+          <t>Lincolnshire Community Health Services NHS Trust</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RT5</t>
+          <t>RY5</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>lpt.communications@nhs.net</t>
+          <t>ulth.lchscommunications@nhs.net</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>kamy.basra@leicspart.nhs.uk</t>
+          <t>lchsecomms@lincs-chs.nhs.uk</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.leicspart.nhs.uk/contact/comms/</t>
+          <t>https://lincolnshirecommunityhealthservices.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>lpt.foi@nhs.net</t>
+          <t>lhnt.foi.lchs@nhs.net</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FOIrequests@leicspart.nhs.uk</t>
+          <t>agcsu.foi.lchs@nhs.net</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.leicspart.nhs.uk/about/freedom-of-information-requests/</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>FOI handled via shared CSU inbox [2026-08-01] foi_email primary updated 2026-08-01 from https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information; prior value agcsu.foi.lchs@nhs.net moved to _alt.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lewisham and Greenwich NHS Trust</t>
+          <t>Lincolnshire Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RJ2</t>
+          <t>RP7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>lg.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>lpft.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>lincs.spa@nhs.net</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
+          <t>https://www.lpft.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>foi.lg@nhs.net</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>lpft.FOIrequest@nhs.net</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>lpn-tr.FOIrequest@nhs.net</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.lewishamandgreenwich.nhs.uk/contact-us/</t>
+          <t>https://www.lpft.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -3737,491 +3745,475 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Lincolnshire Community Health Services NHS Trust</t>
+          <t>Liverpool Heart and Chest Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RY5</t>
+          <t>RBQ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ulth.lchscommunications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>lchsecomms@lincs-chs.nhs.uk</t>
-        </is>
-      </c>
+          <t>Matthew.Back@lhch.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://lincolnshirecommunityhealthservices.nhs.uk/contact-us</t>
+          <t>https://www.lhch.nhs.uk/press-and-media</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>lhnt.foi.lchs@nhs.net</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>agcsu.foi.lchs@nhs.net</t>
-        </is>
-      </c>
+          <t>FOIRequests@lhch.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information</t>
+          <t>https://www.lhch.nhs.uk/make-a-request</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>FOI handled via shared CSU inbox [2026-08-01] foi_email primary updated 2026-08-01 from https://lincolnshirecommunityhealthservices.nhs.uk/about-us/freedom-of-information; prior value agcsu.foi.lchs@nhs.net moved to _alt.</t>
+          <t>Press contact is named individual (Head of Communications) - no shared press inbox published</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lincolnshire Partnership NHS Foundation Trust</t>
+          <t>Liverpool University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RP7</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>lpft.communications@nhs.net</t>
+          <t>Communications@uhliverpool.nhs.uk</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>lincs.spa@nhs.net</t>
+          <t>communications@liverpoolft.nhs.uk</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.lpft.nhs.uk/contact-us</t>
+          <t>https://www.uhliverpool.nhs.uk/contact-us/press-information</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>lpft.FOIrequest@nhs.net</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>lpn-tr.FOIrequest@nhs.net</t>
-        </is>
-      </c>
+          <t>FOIRequests@liverpoolft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.lpft.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>https://www.uhliverpool.nhs.uk/contact-us/freedom-information-requests</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>now part of NHS University Hospitals of Liverpool Group</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Liverpool Heart and Chest Hospital NHS Foundation Trust</t>
+          <t>Liverpool Women's NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RBQ</t>
+          <t>REP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Matthew.Back@lhch.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Communications@uhliverpool.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>communications@lwh.nhs.uk</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.lhch.nhs.uk/press-and-media</t>
+          <t>https://www.uhliverpool.nhs.uk/contact-us/press-information</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FOIRequests@lhch.nhs.uk</t>
+          <t>FOI@lwh.nhs.uk</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.lhch.nhs.uk/make-a-request</t>
+          <t>https://www.uhliverpool.nhs.uk/freedom-information-requests-lwh</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Press contact is named individual (Head of Communications) - no shared press inbox published</t>
+          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme | foi_source_url updated 2026-07-18 to live UHL group FOI page (FOI@lwh.nhs.uk confirmed); prior liverpoolwomens.nhs.uk PDF now redirects to the group site. Group submission inbox FOIRequests@liverpoolft.nhs.uk also seen (not adopted as primary)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Liverpool University Hospitals NHS Foundation Trust</t>
+          <t>London Ambulance Service NHS Trust</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>RRU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Communications@uhliverpool.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>communications@liverpoolft.nhs.uk</t>
-        </is>
-      </c>
+          <t>londamb.press.office@nhs.net</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.uhliverpool.nhs.uk/contact-us/press-information</t>
+          <t>https://www.londonambulance.nhs.uk/news-2/follow-us-social-media/</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FOIRequests@liverpoolft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>londamb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>foi@londonambulance.nhs.uk</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.uhliverpool.nhs.uk/contact-us/freedom-information-requests</t>
+          <t>https://www.londonambulance.nhs.uk/talking-with-us/freedom-of-information/classes-of-information/</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>now part of NHS University Hospitals of Liverpool Group</t>
+          <t>2026-08-22: foi_email cleaned to londamb.foi@nhs.net - the stored value carried a '?subject=...' mailto querystring that is not part of the address; address itself re-confirmed against published LAS FOI responses. Press address re-confirmed by decoding the cfemail token on the press page.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Liverpool Women's NHS Foundation Trust</t>
+          <t>London North West University Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>REP</t>
+          <t>R1K</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Communications@uhliverpool.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>communications@lwh.nhs.uk</t>
-        </is>
-      </c>
+          <t>lnwh-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.uhliverpool.nhs.uk/contact-us/press-information</t>
+          <t>https://www.lnwh.nhs.uk/press</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FOI@lwh.nhs.uk</t>
+          <t>lnwh@infreemation.co.uk</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.uhliverpool.nhs.uk/freedom-information-requests-lwh</t>
+          <t>https://www.lnwh.nhs.uk/foi</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Liverpool Women's now part of NHS University Hospitals of Liverpool Group; legacy LWH FOI inbox still in use per FOI publication scheme | foi_source_url updated 2026-07-18 to live UHL group FOI page (FOI@lwh.nhs.uk confirmed); prior liverpoolwomens.nhs.uk PDF now redirects to the group site. Group submission inbox FOIRequests@liverpoolft.nhs.uk also seen (not adopted as primary)</t>
+          <t>FOI uses third-party Infreemation portal</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>London Ambulance Service NHS Trust</t>
+          <t>Maidstone and Tunbridge Wells NHS Trust</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RRU</t>
+          <t>RWF</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>londamb.press.office@nhs.net</t>
+          <t>mtw-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.londonambulance.nhs.uk/news-2/follow-us-social-media/</t>
+          <t>https://www.mtw.nhs.uk/news/media-enquiries-and-contacts/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>londamb.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>foi@londonambulance.nhs.uk</t>
-        </is>
-      </c>
+          <t>mtw-tr.FOIadmin@nhs.net</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.londonambulance.nhs.uk/talking-with-us/freedom-of-information/classes-of-information/</t>
+          <t>https://www.mtw.nhs.uk/freedom-of-information/</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-08-22: foi_email cleaned to londamb.foi@nhs.net - the stored value carried a '?subject=...' mailto querystring that is not part of the address; address itself re-confirmed against published LAS FOI responses. Press address re-confirmed by decoding the cfemail token on the press page.</t>
+          <t>2026-07-04: source URLs refreshed (old /contact/ now 404); FOI mtw-tr.foiadmin@nhs.net confirmed live, press email unchanged (media page blocks automated fetch).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>London North West University Healthcare NHS Trust</t>
+          <t>Manchester University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>R1K</t>
+          <t>R0A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>lnwh-tr.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>pressoffice@mft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>communications@mft.nhs.uk</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.lnwh.nhs.uk/press</t>
+          <t>https://mft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>lnwh@infreemation.co.uk</t>
+          <t>foi@mft.nhs.uk</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.lnwh.nhs.uk/foi</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>FOI uses third-party Infreemation portal</t>
-        </is>
-      </c>
+          <t>https://mft.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Maidstone and Tunbridge Wells NHS Trust</t>
+          <t>Medway NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RWF</t>
+          <t>RPA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mtw-tr.communications@nhs.net</t>
+          <t>communications.medwayft@nhs.net</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/news/media-enquiries-and-contacts/</t>
+          <t>https://www.medway.nhs.uk/contact-us/media-and-website-enquiries/</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>mtw-tr.FOIadmin@nhs.net</t>
+          <t>medwayft.foi@nhs.net</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/freedom-of-information/</t>
+          <t>https://www.medway.nhs.uk/about-us/access-to-information/</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-07-04: source URLs refreshed (old /contact/ now 404); FOI mtw-tr.foiadmin@nhs.net confirmed live, press email unchanged (media page blocks automated fetch).</t>
+          <t>Medway contact page does not list emails</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Manchester University NHS Foundation Trust</t>
+          <t>Mersey Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>R0A</t>
+          <t>RW4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>pressoffice@mft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>communications@mft.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications@merseycare.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://mft.nhs.uk/contact-us/</t>
+          <t>https://www.merseycare.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>foi@mft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>FOI@merseycare.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>freedomofinformation@merseycare.nhs.uk</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://mft.nhs.uk/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>https://www.merseycare.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>press email not found on site; FOI email not found on site; Mersey Care: all contact and FOI URLs tested returned 403 (bot block). Could not verify.; Verified via Playwright 4 May 2026 (WebFetch had been blocked by Cloudflare).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Medway NHS Foundation Trust</t>
+          <t>Mersey and West Lancashire Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RPA</t>
+          <t>RBN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>communications.medwayft@nhs.net</t>
+          <t>communications@merseywestlancs.nhs.uk</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.medway.nhs.uk/contact-us/media-and-website-enquiries/</t>
+          <t>https://www.merseywestlancs.nhs.uk/media-and-pr</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>medwayft.foi@nhs.net</t>
+          <t>foirequests@merseywestlancs.nhs.uk</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.medway.nhs.uk/about-us/access-to-information/</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Medway contact page does not list emails</t>
-        </is>
-      </c>
+          <t>https://www.merseywestlancs.nhs.uk/foi</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mersey Care NHS Foundation Trust</t>
+          <t>Mid Cheshire Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RW4</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>communications@merseycare.nhs.uk</t>
+          <t>communications@mcht.nhs.uk</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.merseycare.nhs.uk/contact-us</t>
+          <t>https://www.mcht.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FOI@merseycare.nhs.uk</t>
+          <t>foi.foi@mcht.nhs.uk</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>freedomofinformation@merseycare.nhs.uk</t>
+          <t>foi@mcht.nhs.uk</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.merseycare.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>press email not found on site; FOI email not found on site; Mersey Care: all contact and FOI URLs tested returned 403 (bot block). Could not verify.; Verified via Playwright 4 May 2026 (WebFetch had been blocked by Cloudflare).</t>
-        </is>
-      </c>
+          <t>https://www.mcht.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mersey and West Lancashire Teaching Hospitals NHS Trust</t>
+          <t>Mid Yorkshire Teaching NHS Trust</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RBN</t>
+          <t>RXF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>communications@merseywestlancs.nhs.uk</t>
+          <t>midyorks.communications@nhs.net</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.merseywestlancs.nhs.uk/media-and-pr</t>
+          <t>https://www.midyorks.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>foirequests@merseywestlancs.nhs.uk</t>
+          <t>midyorks.foi@nhs.net</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.merseywestlancs.nhs.uk/foi</t>
+          <t>https://www.midyorks.nhs.uk/publication-scheme</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -4229,38 +4221,34 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mid Cheshire Hospitals NHS Foundation Trust</t>
+          <t>Mid and South Essex NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>RAJ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>communications@mcht.nhs.uk</t>
+          <t>mse.communications@nhs.net</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.mcht.nhs.uk/contact-us</t>
+          <t>https://www.mse.nhs.uk/media-centre</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>foi.foi@mcht.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>foi@mcht.nhs.uk</t>
-        </is>
-      </c>
+          <t>mse.foi.suhft@nhs.net</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.mcht.nhs.uk/contact-us</t>
+          <t>https://www.mse.nhs.uk/freedom-of-information</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4268,311 +4256,323 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mid Yorkshire Teaching NHS Trust</t>
+          <t>Midlands Partnership University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RXF</t>
+          <t>RRE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>midyorks.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>communications@mpft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>enquiries@mpft.nhs.uk</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.midyorks.nhs.uk/contact-us/</t>
+          <t>https://www.mpft.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>midyorks.foi@nhs.net</t>
+          <t>foi@mpft.nhs.uk</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.midyorks.nhs.uk/publication-scheme</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>https://www.mpft.nhs.uk/about-us/freedom-information</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>MPFT FOI page directs requests via postal address or online portal (mpft.ams-sar.com); no FOI email published. | foi_source_url set 2026-06-06 from live FOI page (no email published; FOI via online Access Request Portal); existing foi@mpft.nhs.uk retained.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mid and South Essex NHS Foundation Trust</t>
+          <t>Milton Keynes University Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RAJ</t>
+          <t>RD8</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mse.communications@nhs.net</t>
+          <t>communications@mkuh.nhs.uk</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.mse.nhs.uk/media-centre</t>
+          <t>https://www.mkuh.nhs.uk/news/information-for-the-media</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>mse.foi.suhft@nhs.net</t>
+          <t>Foi.PublicationSchemeCo-ordinator@mkuh.nhs.uk</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.mse.nhs.uk/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>https://www.mkuh.nhs.uk/about-us/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Live site behind Cloudflare bot challenge; values decoded from CloudFlare cfemail in Wayback Machine snapshot Dec 2024</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Midlands Partnership University NHS Foundation Trust</t>
+          <t>Moorfields Eye Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RRE</t>
+          <t>RP6</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>communications@mpft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>enquiries@mpft.nhs.uk</t>
-        </is>
-      </c>
+          <t>Moorfields.pressoffice@nhs.net</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.mpft.nhs.uk/contact-us</t>
+          <t>https://www.moorfields.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>foi@mpft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>Moorfields.webrequests@nhs.net</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>moorfields.fois@nhs.net</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.mpft.nhs.uk/about-us/freedom-information</t>
+          <t>https://www.moorfields.nhs.uk/about-us/resources/freedom-of-information</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>MPFT FOI page directs requests via postal address or online portal (mpft.ams-sar.com); no FOI email published. | foi_source_url set 2026-06-06 from live FOI page (no email published; FOI via online Access Request Portal); existing foi@mpft.nhs.uk retained.</t>
+          <t>FOI page lists webrequests inbox; may be IG-handled rather than dedicated FOI | foi_source_url corrected 2026-06-06 (old about-us/freedom-of-information now 404); live page shows moorfields.fois@nhs.net (= existing _alt); primary Moorfields.webrequests@nhs.net retained.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Milton Keynes University Hospital NHS Foundation Trust</t>
+          <t>East of England Community Health and Care NHS Trust</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RD8</t>
+          <t>RY3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>communications@mkuh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>eec.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ccs.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.mkuh.nhs.uk/news/information-for-the-media</t>
+          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Foi.PublicationSchemeCo-ordinator@mkuh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>eec.accesstoinfo@nhs.net</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ccs.accesstoinfo@nhs.net</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.mkuh.nhs.uk/about-us/freedom-of-information</t>
+          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Live site behind Cloudflare bot challenge; values decoded from CloudFlare cfemail in Wayback Machine snapshot Dec 2024</t>
+          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV); press and FOI primaries updated 2026-08-08 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us — the merged trust now publishes eec.communications@nhs.net (media) and eec.accesstoinfo@nhs.net (FOI); prior values ccs.communications@nhs.net and ccs.accesstoinfo@nhs.net moved to the _alt fields, displacing the legacy Norfolk Community addresses Communications@nchc.nhs.uk and FreedomOfInformationProvider@nchc.nhs.uk, which are recorded here so they are not lost</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Moorfields Eye Hospital NHS Foundation Trust</t>
+          <t>Norfolk and Norwich University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RP6</t>
+          <t>RM1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Moorfields.pressoffice@nhs.net</t>
+          <t>communications@nnuh.nhs.uk</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.moorfields.nhs.uk/contact-us</t>
+          <t>https://www.nnuh.nhs.uk/news-and-events/media-centre/contacting-the-communications-team/</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Moorfields.webrequests@nhs.net</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>moorfields.fois@nhs.net</t>
-        </is>
-      </c>
+          <t>foi@nnuh.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.moorfields.nhs.uk/about-us/resources/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>FOI page lists webrequests inbox; may be IG-handled rather than dedicated FOI | foi_source_url corrected 2026-06-06 (old about-us/freedom-of-information now 404); live page shows moorfields.fois@nhs.net (= existing _alt); primary Moorfields.webrequests@nhs.net retained.</t>
-        </is>
-      </c>
+          <t>https://www.nnuh.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>East of England Community Health and Care NHS Trust</t>
+          <t>Norfolk and Suffolk NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>RY3</t>
+          <t>RMY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>eec.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ccs.communications@nhs.net</t>
-        </is>
-      </c>
+          <t>media@nsft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
+          <t>https://www.nsft.nhs.uk/press</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>eec.accesstoinfo@nhs.net</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>ccs.accesstoinfo@nhs.net</t>
-        </is>
-      </c>
+          <t>informationrights@nsft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Norfolk Community merged into East of England Community Health &amp; Care; shared CCS inbox; renamed from 'Norfolk Community Health and Care NHS Trust' on 2026-05-16 after April 2026 merger with Cambridgeshire Community Services (RYV); press and FOI primaries updated 2026-08-08 from https://eastofenglandcommunityhealthandcare.nhs.uk/contact-us — the merged trust now publishes eec.communications@nhs.net (media) and eec.accesstoinfo@nhs.net (FOI); prior values ccs.communications@nhs.net and ccs.accesstoinfo@nhs.net moved to the _alt fields, displacing the legacy Norfolk Community addresses Communications@nchc.nhs.uk and FreedomOfInformationProvider@nchc.nhs.uk, which are recorded here so they are not lost</t>
-        </is>
-      </c>
+          <t>https://www.nsft.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Norfolk and Norwich University Hospitals NHS Foundation Trust</t>
+          <t>North Cumbria Integrated Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RM1</t>
+          <t>RNN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>communications@nnuh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>communications@ncic.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>communications.helpdesk@ncic.nhs.uk</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.nnuh.nhs.uk/news-and-events/media-centre/contacting-the-communications-team/</t>
+          <t>https://www.ncic.nhs.uk/contact</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>foi@nnuh.nhs.uk</t>
+          <t>FOIRequests@ncic.nhs.uk</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.nnuh.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>https://www.ncic.nhs.uk/patients-visitors/patient-information-leaflets/freedom-information</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>FOI page not located; North Cumbria FOI URLs all 404; contact page references FOI but only via submission portal. | foi_source_url located 2026-06-06; live page confirms FOIRequests@ncic.nhs.uk (matches primary).</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Norfolk and Suffolk NHS Foundation Trust</t>
+          <t>North East Ambulance Service NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RMY</t>
+          <t>RX6</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>media@nsft.nhs.uk</t>
+          <t>publicrelations@neas.nhs.uk</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.nsft.nhs.uk/press</t>
+          <t>https://www.neas.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>informationrights@nsft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+          <t>Freedom.Of.Information.Requests@neas.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>publicrelations@neas.nhs.uk</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.nsft.nhs.uk/freedom-of-information/</t>
+          <t>https://www.neas.nhs.uk/about-us/freedom-information</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -4580,38 +4580,42 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>North Bristol NHS Trust</t>
+          <t>North East London NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RVJ</t>
+          <t>RAT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>nbtcommunications@nbt.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>press@nelft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>communications@nelft.nhs.uk</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.nbt.nhs.uk/about-us/contact-us</t>
+          <t>https://www.nelft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FOIArequests@nbt.nhs.uk</t>
+          <t>foi.foi@nelft.nhs.uk</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>foi@nbt.nhs.uk</t>
+          <t>foi@nelft.nhs.uk</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.nbt.nhs.uk/about-us/freedom-information</t>
+          <t>https://www.nelft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -4619,280 +4623,276 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>North Cumbria Integrated Care NHS Foundation Trust</t>
+          <t>North Staffordshire Combined Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RNN</t>
+          <t>RLY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>communications@ncic.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>communications.helpdesk@ncic.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications@combined.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.ncic.nhs.uk/contact</t>
+          <t>https://www.combined.nhs.uk/contact/contact-us/</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FOIRequests@ncic.nhs.uk</t>
+          <t>FOIRequests@combined.nhs.uk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.ncic.nhs.uk/patients-visitors/patient-information-leaflets/freedom-information</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>FOI page not located; North Cumbria FOI URLs all 404; contact page references FOI but only via submission portal. | foi_source_url located 2026-06-06; live page confirms FOIRequests@ncic.nhs.uk (matches primary).</t>
+          <t>FOI page returned 404 from tested paths and connection reset on combined.nhs.uk; FOI inbox not retrievable; North Staffordshire Combined FOI sub-pages 404; no FOI email published on contact page.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>North East Ambulance Service NHS Foundation Trust</t>
+          <t>North Tees and Hartlepool NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RX6</t>
+          <t>RVW</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>publicrelations@neas.nhs.uk</t>
+          <t>nth-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.neas.nhs.uk/contact-us</t>
+          <t>https://www.nth.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Freedom.Of.Information.Requests@neas.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>publicrelations@neas.nhs.uk</t>
-        </is>
-      </c>
+          <t>nth-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.neas.nhs.uk/about-us/freedom-information</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>https://www.nth.nhs.uk/contact/</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Both emails obscured by Cloudflare email-protection on the pages</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>North East London NHS Foundation Trust</t>
+          <t>North West Ambulance Service NHS Trust</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RAT</t>
+          <t>RX7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>press@nelft.nhs.uk</t>
+          <t>press@nwas.nhs.uk</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>communications@nelft.nhs.uk</t>
+          <t>press.office@nwas.nhs.uk</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://www.nelft.nhs.uk/contact-us/</t>
+          <t>https://www.nwas.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>foi.foi@nelft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>foi@nelft.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi.enquiries@nwas.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.nelft.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>https://www.nwas.nhs.uk/foi/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Cloudflare email-protection decoded for FOI</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>North Staffordshire Combined Healthcare NHS Trust</t>
+          <t>North West Anglia NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>RLY</t>
+          <t>RGN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>communications@combined.nhs.uk</t>
+          <t>nwangliaft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://www.combined.nhs.uk/contact/contact-us/</t>
+          <t>https://www.nwangliaft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FOIRequests@combined.nhs.uk</t>
+          <t>nwangliaft.FOITeam@nhs.net</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>FOI page returned 404 from tested paths and connection reset on combined.nhs.uk; FOI inbox not retrievable; North Staffordshire Combined FOI sub-pages 404; no FOI email published on contact page.</t>
-        </is>
-      </c>
+          <t>https://www.nwangliaft.nhs.uk/freedom-of-information-foi-requests</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>North Tees and Hartlepool NHS Foundation Trust</t>
+          <t>Northampton General Hospital NHS Trust</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>RVW</t>
+          <t>RNS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>nth-tr.communications@nhs.net</t>
+          <t>ngh-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://www.nth.nhs.uk/contact/</t>
+          <t>https://www.northamptongeneral.nhs.uk/Services/Our-Non-Clinical-Services-and-Departments/Communications.aspx</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>nth-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
+          <t>ngh-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>foi@ngh.nhs.uk</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.nth.nhs.uk/contact/</t>
+          <t>https://www.northamptongeneral.nhs.uk/About/Information-and-Data-Protection/Freedom-of-Information-Act/Freedom-of-Information-Act-2000/Publication-Scheme/Publication-Scheme.aspx</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Both emails obscured by Cloudflare email-protection on the pages</t>
+          <t>FOI email retrieved via Wayback snapshot of publication scheme page 2026-07-04: press source URL refreshed (old News/Communications-team.aspx 404); ngh-tr.communications@nhs.net re-confirmed.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>North West Ambulance Service NHS Trust</t>
+          <t>Northamptonshire Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RX7</t>
+          <t>RP1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>press@nwas.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>press.office@nwas.nhs.uk</t>
-        </is>
-      </c>
+          <t>commsteam@nhft.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://www.nwas.nhs.uk/contact-us/</t>
+          <t>https://www.nhft.nhs.uk/contact</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>foi.enquiries@nwas.nhs.uk</t>
+          <t>foi@nhft.nhs.uk</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.nwas.nhs.uk/foi/</t>
+          <t>https://www.nhft.nhs.uk/foi/</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Cloudflare email-protection decoded for FOI</t>
+          <t>FOI page not located</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>North West Anglia NHS Foundation Trust</t>
+          <t>Northern Care Alliance NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RGN</t>
+          <t>RM3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>nwangliaft.communications@nhs.net</t>
+          <t>trust.communications@nca.nhs.uk</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://www.nwangliaft.nhs.uk/contact-us/</t>
+          <t>https://www.northerncarealliance.nhs.uk/about-us/media-centre</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>nwangliaft.FOITeam@nhs.net</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
+          <t>FreedomofInformationRequests@nca.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>penninefoi.atsalford@srft.nhs.uk</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.nwangliaft.nhs.uk/freedom-of-information-foi-requests</t>
+          <t>https://www.northerncarealliance.nhs.uk/contact-us/freedom-information-requests</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -4900,284 +4900,280 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Northampton General Hospital NHS Trust</t>
+          <t>Northern Lincolnshire and Goole NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RNS</t>
+          <t>RJL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ngh-tr.communications@nhs.net</t>
+          <t>nlg-tr.comms@nhs.net</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://www.northamptongeneral.nhs.uk/Services/Our-Non-Clinical-Services-and-Departments/Communications.aspx</t>
+          <t>https://www.nlg.nhs.uk/press-and-media/</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ngh-tr.foi@nhs.net</t>
+          <t>nlg-tr.nlagfoi@nhs.net</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>foi@ngh.nhs.uk</t>
+          <t>nlg-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.northamptongeneral.nhs.uk/About/Information-and-Data-Protection/Freedom-of-Information-Act/Freedom-of-Information-Act-2000/Publication-Scheme/Publication-Scheme.aspx</t>
+          <t>https://www.nlg.nhs.uk/foi/</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>FOI email retrieved via Wayback snapshot of publication scheme page 2026-07-04: press source URL refreshed (old News/Communications-team.aspx 404); ngh-tr.communications@nhs.net re-confirmed.</t>
+          <t>Decoded from CloudFlare cfemail data attributes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Northamptonshire Healthcare NHS Foundation Trust</t>
+          <t>Northumbria Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RP1</t>
+          <t>RTF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>commsteam@nhft.nhs.uk</t>
+          <t>media@northumbria-healthcare.nhs.uk</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://www.nhft.nhs.uk/contact</t>
+          <t>https://www.northumbria.nhs.uk/media-centre/contact-us</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>foi@nhft.nhs.uk</t>
+          <t>foi@northumbria.nhs.uk</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.nhft.nhs.uk/foi/</t>
+          <t>https://www.northumbria.nhs.uk/about-us/corporate-information/freedom-information</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>FOI page not located</t>
+          <t>FOI page not located; contact form references FOI option only</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Northern Care Alliance NHS Foundation Trust</t>
+          <t>Nottingham University Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RM3</t>
+          <t>RX1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>trust.communications@nca.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>nuhnt.nuhmedia@nhs.net</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NUHMedia@nuh.nhs.uk</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://www.northerncarealliance.nhs.uk/about-us/media-centre</t>
+          <t>https://www.nuh.nhs.uk/media-enquiries/</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FreedomofInformationRequests@nca.nhs.uk</t>
+          <t>nuhnt.dutyin@nhs.net</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>penninefoi.atsalford@srft.nhs.uk</t>
+          <t>FOI@nuh.nhs.uk</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.northerncarealliance.nhs.uk/contact-us/freedom-information-requests</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>https://www.nuh.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Nottingham UH: contact-us, comms and news-media URLs all 404; no public press email surfaced.; press primary updated 2026-05-16 from https://www.nuh.nhs.uk/media-enquiries/; prior value moved to _alt</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Northern Lincolnshire and Goole NHS Foundation Trust</t>
+          <t>Nottinghamshire Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RJL</t>
+          <t>RHA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>nlg-tr.comms@nhs.net</t>
+          <t>communications@nottshc.nhs.uk</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://www.nlg.nhs.uk/press-and-media/</t>
+          <t>https://www.nottinghamshirehealthcare.nhs.uk/press-and-media</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>nlg-tr.nlagfoi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>nlg-tr.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>FOI@nottshc.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.nlg.nhs.uk/foi/</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Decoded from CloudFlare cfemail data attributes</t>
-        </is>
-      </c>
+          <t>https://www.nottinghamshirehealthcare.nhs.uk/freedom-of-information-request-form</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Northumbria Healthcare NHS Foundation Trust</t>
+          <t>Oxford Health NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RTF</t>
+          <t>RNU</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>media@northumbria-healthcare.nhs.uk</t>
+          <t>Communications.Team@oxfordhealth.nhs.uk</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://www.northumbria.nhs.uk/media-centre/contact-us</t>
+          <t>https://oxfordhealth.nhs.uk/contacts/media-enquiries/</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>foi@northumbria.nhs.uk</t>
+          <t>foiarfi@oxfordhealth.nhs.uk</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.northumbria.nhs.uk/about-us/corporate-information/freedom-information</t>
+          <t>https://www.oxfordhealth.nhs.uk/contacts/</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>FOI page not located; contact form references FOI option only</t>
+          <t>press email not on main contact pages</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nottingham University Hospitals NHS Trust</t>
+          <t>Oxford University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RX1</t>
+          <t>RTH</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>nuhnt.nuhmedia@nhs.net</t>
+          <t>web.editor@ouh.nhs.uk</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NUHMedia@nuh.nhs.uk</t>
+          <t>media.office@ouh.nhs.uk</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://www.nuh.nhs.uk/media-enquiries/</t>
+          <t>https://www.ouh.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>nuhnt.dutyin@nhs.net</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>FOI@nuh.nhs.uk</t>
-        </is>
-      </c>
+          <t>oxford@infreemation.co.uk</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.nuh.nhs.uk/freedom-of-information/</t>
+          <t>https://www.ouh.nhs.uk/about/foi/request/</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Nottingham UH: contact-us, comms and news-media URLs all 404; no public press email surfaced.; press primary updated 2026-05-16 from https://www.nuh.nhs.uk/media-enquiries/; prior value moved to _alt</t>
+          <t>FOI requests directed to online form, no email; subject.accessrequest@ouh.nhs.uk only for personal data/SAR; Oxford UH FOI page directs requests via online form (foienquiries.ouh.nhs.uk/start-now) and postal address; no generic FOI email published. subject.accessrequest@ouh.nhs.uk is for Subject Access only. | foi_source_url updated 2026-06-27 to live FOI request page; FOI via online form/portal (oxford@infreemation.co.uk), email unchanged</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Nottinghamshire Healthcare NHS Foundation Trust</t>
+          <t>Oxleas NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RHA</t>
+          <t>RPG</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>communications@nottshc.nhs.uk</t>
+          <t>oxl-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://www.nottinghamshirehealthcare.nhs.uk/press-and-media</t>
+          <t>https://www.oxleas.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FOI@nottshc.nhs.uk</t>
+          <t>oxl-tr.FOI@nhs.net</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.nottinghamshirehealthcare.nhs.uk/freedom-of-information-request-form</t>
+          <t>https://www.oxleas.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -5185,116 +5181,116 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Oxford Health NHS Foundation Trust</t>
+          <t>Pennine Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RNU</t>
+          <t>RT2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Communications.Team@oxfordhealth.nhs.uk</t>
+          <t>media.penninecare@nhs.net</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://oxfordhealth.nhs.uk/contacts/media-enquiries/</t>
+          <t>https://www.penninecare.nhs.uk/contact</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>foiarfi@oxfordhealth.nhs.uk</t>
+          <t>foi.penninecare@nhs.net</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.oxfordhealth.nhs.uk/contacts/</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>press email not on main contact pages</t>
-        </is>
-      </c>
+          <t>https://www.penninecare.nhs.uk/contact</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Oxford University Hospitals NHS Foundation Trust</t>
+          <t>Portsmouth Hospitals University National Health Service Trust</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RTH</t>
+          <t>RHU</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>web.editor@ouh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>media.office@ouh.nhs.uk</t>
-        </is>
-      </c>
+          <t>pho-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.ouh.nhs.uk/contact/</t>
+          <t>https://www.porthosp.nhs.uk/about-us/contact-us</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>oxford@infreemation.co.uk</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>pho-tr.foirequest-portsmouth@nhs.net</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Portsmouth.FOIRequests@porthosp.nhs.uk</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.ouh.nhs.uk/about/foi/request/</t>
+          <t>https://www.porthosp.nhs.uk/about-us/information-governance/requesting-information</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>FOI requests directed to online form, no email; subject.accessrequest@ouh.nhs.uk only for personal data/SAR; Oxford UH FOI page directs requests via online form (foienquiries.ouh.nhs.uk/start-now) and postal address; no generic FOI email published. subject.accessrequest@ouh.nhs.uk is for Subject Access only. | foi_source_url updated 2026-06-27 to live FOI request page; FOI via online form/portal (oxford@infreemation.co.uk), email unchanged</t>
+          <t>2026-08-18: press_email pho-tr.communications@nhs.net re-verified against the trust's own contact-us page. Stale alt communications@porthosp.nhs.uk removed - reported as wrong. Note: Isle of Wight NHS Trust (R1F) legitimately shares this same comms inbox.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Oxleas NHS Foundation Trust</t>
+          <t>Queen Victoria Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RPG</t>
+          <t>RPC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>oxl-tr.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>qvh.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>qvh.info@nhs.net</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.oxleas.nhs.uk/contact-us/</t>
+          <t>https://www.qvh.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>oxl-tr.FOI@nhs.net</t>
+          <t>qvh.foi@nhs.net</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.oxleas.nhs.uk/contact-us/</t>
+          <t>https://www.qvh.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -5302,34 +5298,34 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Pennine Care NHS Foundation Trust</t>
+          <t>Rotherham Doncaster and South Humber NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>RT2</t>
+          <t>RXE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>media.penninecare@nhs.net</t>
+          <t>rdash.rdashcommunications@nhs.net</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.penninecare.nhs.uk/contact</t>
+          <t>https://www.rdash.nhs.uk/contact-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>foi.penninecare@nhs.net</t>
+          <t>rdash.foirdash@nhs.net</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.penninecare.nhs.uk/contact</t>
+          <t>https://www.rdash.nhs.uk/about-us/governance/freedom-of-information/</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -5337,81 +5333,73 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Portsmouth Hospitals University National Health Service Trust</t>
+          <t>Royal Berkshire NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RHU</t>
+          <t>RHW</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>pho-tr.communications@nhs.net</t>
+          <t>communications@royalberkshire.nhs.uk</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.porthosp.nhs.uk/about-us/contact-us</t>
+          <t>https://www.royalberkshire.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>pho-tr.foirequest-portsmouth@nhs.net</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Portsmouth.FOIRequests@porthosp.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@royalberkshire.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.porthosp.nhs.uk/about-us/information-governance/requesting-information</t>
+          <t>https://www.royalberkshire.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-08-18: press_email pho-tr.communications@nhs.net re-verified against the trust's own contact-us page. Stale alt communications@porthosp.nhs.uk removed - reported as wrong. Note: Isle of Wight NHS Trust (R1F) legitimately shares this same comms inbox.</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Queen Victoria Hospital NHS Foundation Trust</t>
+          <t>Royal Cornwall Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>RPC</t>
+          <t>REF</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>qvh.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>qvh.info@nhs.net</t>
-        </is>
-      </c>
+          <t>rcht.communication@nhs.net</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.qvh.nhs.uk/contact-us/</t>
+          <t>https://news.royalcornwallhospitals.nhs.uk/press-and-media/</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>qvh.foi@nhs.net</t>
+          <t>rch-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.qvh.nhs.uk/contact-us/</t>
+          <t>https://royalcornwallhospitals.nhs.uk/organisation/freedom-of-information/</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -5419,108 +5407,124 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Rotherham Doncaster and South Humber NHS Foundation Trust</t>
+          <t>Royal Devon University Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RXE</t>
+          <t>RH8</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>rdash.rdashcommunications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>rde-tr.RDEComms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>rduh.comms@nhs.net</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.rdash.nhs.uk/contact-us/media-enquiries/</t>
+          <t>https://www.royaldevon.nhs.uk/get-in-touch</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>rdash.foirdash@nhs.net</t>
+          <t>rduh.foi@nhs.net</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.rdash.nhs.uk/about-us/governance/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>https://www.royaldevon.nhs.uk/about-us/information-governance/freedom-of-information-foi-and-environmental-information-regulations-eir/</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Trust uses two legacy comms inboxes (Eastern: rde-tr.RDEComms@nhs.net; Northern: ndht.Communications@nhs.net) post-merger</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Royal Berkshire NHS Foundation Trust</t>
+          <t>Royal Free London NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>RHW</t>
+          <t>RAL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>communications@royalberkshire.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>rf-tr.mediaenquiries@nhs.net</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>tr-rf.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.royalberkshire.nhs.uk/contact-us/</t>
+          <t>https://www.royalfree.nhs.uk/contact-us/contact-media-team</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>foi@royalberkshire.nhs.uk</t>
+          <t>rf-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.royalberkshire.nhs.uk/contact-us/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page.</t>
+          <t>Site (incl FOI page) returned 403 to scraping; press email confirmed via search results. FOI email not extractable - likely rf-tr.foi@nhs.net but unverified; Royal Free FOI page returned 403 to WebFetch on multiple attempts; could not retrieve email. | press primary updated 2026-05-29 from [https://www.royalfree.nhs.uk/contact-us/contact-media-team]; prior value tr-rf.communications@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Royal Cornwall Hospitals NHS Trust</t>
+          <t>Royal National Orthopaedic Hospital NHS Trust</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>REF</t>
+          <t>RAN</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>rcht.communication@nhs.net</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>rnoh.mediaenquiries-sm@nhs.net</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>rnoh.communicationsdept@nhs.net</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.royalcornwallhospitals.nhs.uk/press-and-media/</t>
+          <t>https://www.rnoh.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>rch-tr.foi@nhs.net</t>
+          <t>rnoh.foi-sm@nhs.net</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://royalcornwallhospitals.nhs.uk/organisation/freedom-of-information/</t>
+          <t>https://www.rnoh.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -5528,354 +5532,350 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Royal Devon University Healthcare NHS Foundation Trust</t>
+          <t>Royal Papworth Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>RH8</t>
+          <t>RGM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>rde-tr.RDEComms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>rduh.comms@nhs.net</t>
-        </is>
-      </c>
+          <t>papworth.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.royaldevon.nhs.uk/get-in-touch</t>
+          <t>https://royalpapworth.nhs.uk/contact/media-enquiries</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>rduh.foi@nhs.net</t>
+          <t>papworth.foidept@nhs.net</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.royaldevon.nhs.uk/about-us/information-governance/freedom-of-information-foi-and-environmental-information-regulations-eir/</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Trust uses two legacy comms inboxes (Eastern: rde-tr.RDEComms@nhs.net; Northern: ndht.Communications@nhs.net) post-merger</t>
-        </is>
-      </c>
+          <t>https://royalpapworth.nhs.uk/our-hospital/information-we-publish/freedom-information</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Royal Free London NHS Foundation Trust</t>
+          <t>Royal Surrey County Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>RAL</t>
+          <t>RA2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>rf-tr.mediaenquiries@nhs.net</t>
+          <t>rsch.pressoffice@nhs.net</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>tr-rf.communications@nhs.net</t>
+          <t>rsch.communications@nhs.net</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.royalfree.nhs.uk/contact-us/contact-media-team</t>
+          <t>https://www.royalsurrey.nhs.uk/useful-contacts-/</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>rf-tr.foi@nhs.net</t>
+          <t>rsc-tr.FreedomOfInformation@nhs.net</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Site (incl FOI page) returned 403 to scraping; press email confirmed via search results. FOI email not extractable - likely rf-tr.foi@nhs.net but unverified; Royal Free FOI page returned 403 to WebFetch on multiple attempts; could not retrieve email. | press primary updated 2026-05-29 from [https://www.royalfree.nhs.uk/contact-us/contact-media-team]; prior value tr-rf.communications@nhs.net moved to _alt</t>
-        </is>
-      </c>
+          <t>https://www.royalsurrey.nhs.uk/how-to-make-a-freedom-of-information-request</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Royal National Orthopaedic Hospital NHS Trust</t>
+          <t>Royal United Hospitals Bath NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>RAN</t>
+          <t>RD1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>rnoh.mediaenquiries-sm@nhs.net</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>rnoh.communicationsdept@nhs.net</t>
-        </is>
-      </c>
+          <t>ruh-tr.CommunicationTeam@nhs.net</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.rnoh.nhs.uk/contact-us</t>
+          <t>https://www.ruh.nhs.uk/media/index.asp</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>rnoh.foi-sm@nhs.net</t>
+          <t>ruh-tr.FOIRequests@nhs.net</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.rnoh.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>https://www.ruh.nhs.uk/foi/overview_obtain_information.asp?menu_id=1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>FOI page references comms team but no dedicated FOI email surfaced; Royal United Bath FOI URL not retrieved (legacy .asp paths).</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Royal Papworth Hospital NHS Foundation Trust</t>
+          <t>Salisbury NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>RGM</t>
+          <t>RNZ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>papworth.communications@nhs.net</t>
+          <t>dave.roberts@nhs.net</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://royalpapworth.nhs.uk/contact/media-enquiries</t>
+          <t>https://www.salisbury.nhs.uk/about-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>papworth.foidept@nhs.net</t>
+          <t>sft.freedomofinformation@nhs.net</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://royalpapworth.nhs.uk/our-hospital/information-we-publish/freedom-information</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>https://www.salisbury.nhs.uk/about-us/freedom-of-information-foi/how-to-make-a-request/</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Salisbury press contacts are individuals only (Dave Roberts and Lydia.Davies6@nhs.net); no team mailbox listed</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Royal Surrey County Hospital NHS Foundation Trust</t>
+          <t>Sandwell and West Birmingham Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>RA2</t>
+          <t>RXK</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>rsch.pressoffice@nhs.net</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>rsch.communications@nhs.net</t>
-        </is>
-      </c>
+          <t>swbh.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://www.royalsurrey.nhs.uk/useful-contacts-/</t>
+          <t>https://www.swbh.nhs.uk/news/</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>rsc-tr.FreedomOfInformation@nhs.net</t>
+          <t>swb-tr.SWBH-GM-FOIRequests@nhs.net</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.royalsurrey.nhs.uk/how-to-make-a-freedom-of-information-request</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>https://www.swbh.nhs.uk/our-trust/statutory-information/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Press email confirmed via news team contact section.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Royal United Hospitals Bath NHS Foundation Trust</t>
+          <t>Sheffield Children's NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RD1</t>
+          <t>RCU</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ruh-tr.CommunicationTeam@nhs.net</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>scn-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>communications@sch.nhs.uk</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://www.ruh.nhs.uk/media/index.asp</t>
+          <t>https://www.sheffieldchildrens.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ruh-tr.FOIRequests@nhs.net</t>
+          <t>scn-tr.schfoi@nhs.net</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.ruh.nhs.uk/foi/overview_obtain_information.asp?menu_id=1</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>FOI page references comms team but no dedicated FOI email surfaced; Royal United Bath FOI URL not retrieved (legacy .asp paths).</t>
-        </is>
-      </c>
+          <t>https://www.sheffieldchildrens.nhs.uk/contact-us/</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Salisbury NHS Foundation Trust</t>
+          <t>Sheffield Health and Social Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>RNZ</t>
+          <t>TAH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>dave.roberts@nhs.net</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>communications@sheffieldpartnership.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>communications.shsc@shsc.nhs.uk</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://www.salisbury.nhs.uk/about-us/media-enquiries/</t>
+          <t>https://www.sheffieldpartnership.nhs.uk/contact-us/media-enquiries</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>sft.freedomofinformation@nhs.net</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
+          <t>shpu@infreemation.co.uk</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>shsc@infreemation.co.uk</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.salisbury.nhs.uk/about-us/freedom-of-information-foi/how-to-make-a-request/</t>
+          <t>https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Salisbury press contacts are individuals only (Dave Roberts and Lydia.Davies6@nhs.net); no team mailbox listed</t>
+          <t>Sheffield Health &amp; Social Care rebranded as Sheffield Partnership University FT; FOI uses Infreemation portal | foi primary updated 2026-05-29 from [https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests]; prior value shsc@infreemation.co.uk moved to _alt</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sandwell and West Birmingham Hospitals NHS Trust</t>
+          <t>Sheffield Teaching Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RXK</t>
+          <t>RHQ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>swbh.comms@nhs.net</t>
+          <t>sth.allcommunicationsteam@nhs.net</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://www.swbh.nhs.uk/news/</t>
+          <t>https://www.sth.nhs.uk/news/media-enquiries/</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>swb-tr.SWBH-GM-FOIRequests@nhs.net</t>
+          <t>sth.foi@nhs.net</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.swbh.nhs.uk/our-trust/statutory-information/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Press email confirmed via news team contact section.</t>
-        </is>
-      </c>
+          <t>https://www.sth.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sheffield Children's NHS Foundation Trust</t>
+          <t>Sherwood Forest Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RCU</t>
+          <t>RK5</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>scn-tr.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>communications@sch.nhs.uk</t>
-        </is>
-      </c>
+          <t>sfh-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.sheffieldchildrens.nhs.uk/contact-us/</t>
+          <t>https://www.sfh-tr.nhs.uk/about-us/contact-us/communications-team/</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>scn-tr.schfoi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
+          <t>sfh-tr.information.governance@nhs.net</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>sfh-tr.foi.requests@nhs.net</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.sheffieldchildrens.nhs.uk/contact-us/</t>
+          <t>https://www.sfh-tr.nhs.uk/about-us/regulatory-information/freedom-of-information/</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -5883,366 +5883,362 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sheffield Health and Social Care NHS Foundation Trust</t>
+          <t>Shropshire Community Health NHS Trust</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TAH</t>
+          <t>R1D</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>communications@sheffieldpartnership.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>communications.shsc@shsc.nhs.uk</t>
-        </is>
-      </c>
+          <t>shropcom.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.sheffieldpartnership.nhs.uk/contact-us/media-enquiries</t>
+          <t>https://www.shropscommunityhealth.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>shpu@infreemation.co.uk</t>
+          <t>shropcom.FOIR@infreemation.co.uk</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>shsc@infreemation.co.uk</t>
+          <t>shropcom.foi@nhs.net</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests</t>
+          <t>https://www.shropscommunityhealth.nhs.uk/foi</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Sheffield Health &amp; Social Care rebranded as Sheffield Partnership University FT; FOI uses Infreemation portal | foi primary updated 2026-05-29 from [https://www.sheffieldpartnership.nhs.uk/contact-us/freedom-information-requests]; prior value shsc@infreemation.co.uk moved to _alt</t>
+          <t>FOI uses third-party Infreemation portal | 2026-08-22: contact and FOI pages could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); shropcom.FOIR@infreemation.co.uk corroborated against a 2026 Wayback snapshot, addresses left unchanged.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sheffield Teaching Hospitals NHS Foundation Trust</t>
+          <t>Somerset NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RHQ</t>
+          <t>RH5</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sth.allcommunicationsteam@nhs.net</t>
+          <t>communications@somersetft.nhs.uk</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://www.sth.nhs.uk/news/media-enquiries/</t>
+          <t>https://www.somersetft.nhs.uk/about-us/about-us/news-and-media/</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>sth.foi@nhs.net</t>
+          <t>foi@somersetft.nhs.uk</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.sth.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>https://www.somersetft.nhs.uk/about-us/about-us/publication-scheme/freedom-of-information-foi/</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>press email not located on public pages</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sherwood Forest Hospitals NHS Foundation Trust</t>
+          <t>South Central Ambulance Service NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RK5</t>
+          <t>RYE</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>sfh-tr.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>scas.oncallmedia@nhs.net</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>oncallmedia@scas.nhs.uk</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://www.sfh-tr.nhs.uk/about-us/contact-us/communications-team/</t>
+          <t>https://www.scas.nhs.uk/contact-us/contact-the-media-team/</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>sfh-tr.information.governance@nhs.net</t>
+          <t>scas.foi2@nhs.net</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>sfh-tr.foi.requests@nhs.net</t>
+          <t>foi@scas.nhs.uk</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.sfh-tr.nhs.uk/about-us/regulatory-information/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+          <t>https://www.scas.nhs.uk/contact-us/</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>primary updated 2026-08-22 from https://www.scas.nhs.uk/contact-us/contact-the-media-team/ and https://www.scas.nhs.uk/contact-us/; prior values moved to _alt (press oncallmedia@scas.nhs.uk, foi foi@scas.nhs.uk) - the trust now publishes nhs.net team mailboxes on both pages</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Shropshire Community Health NHS Trust</t>
+          <t>South East Coast Ambulance Service NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>R1D</t>
+          <t>RYD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>shropcom.communications@nhs.net</t>
+          <t>press@secamb.nhs.uk</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://www.shropscommunityhealth.nhs.uk/contact-us</t>
+          <t>https://www.secamb.nhs.uk/news/contact-media-team/</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>shropcom.FOIR@infreemation.co.uk</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>shropcom.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>foi@secamb.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.shropscommunityhealth.nhs.uk/foi</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>FOI uses third-party Infreemation portal | 2026-08-22: contact and FOI pages could not be read from this machine (Imperva/Incapsula shell on plain fetch, server-side WebFetch and headless Playwright); shropcom.FOIR@infreemation.co.uk corroborated against a 2026 Wayback snapshot, addresses left unchanged.</t>
-        </is>
-      </c>
+          <t>https://www.secamb.nhs.uk/freedom-of-information-requests/</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Solent NHS Trust</t>
+          <t>South London and Maudsley NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>R1C</t>
+          <t>RV5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>hiowh.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>communications@solent.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications@slam.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://hiowhealthcare.nhs.uk/contact-us</t>
+          <t>https://www.slam.nhs.uk/newsroom</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>hiowh.freedomofinformation@nhs.net</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>FreedomOfInformation@solent.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@slam.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://hiowhealthcare.nhs.uk/about-us/freedom-information</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Solent merged into Hampshire &amp; Isle of Wight Healthcare NHS FT (1 Oct 2024); FOI email not surfaced on contact page</t>
-        </is>
-      </c>
+          <t>https://www.slam.nhs.uk/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Somerset NHS Foundation Trust</t>
+          <t>South Tees Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RH5</t>
+          <t>RTR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>communications@somersetft.nhs.uk</t>
+          <t>stees.public.relations@nhs.net</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://www.somersetft.nhs.uk/about-us/about-us/news-and-media/</t>
+          <t>https://www.southtees.nhs.uk/press/</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>foi@somersetft.nhs.uk</t>
+          <t>stees.foi.admin@nhs.net</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.somersetft.nhs.uk/about-us/about-us/publication-scheme/freedom-of-information-foi/</t>
+          <t>https://www.southtees.nhs.uk/freedom-of-information-foi/foi-contacts/</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>press email not located on public pages</t>
+          <t>Email addresses obscured by Cloudflare email-protection on both pages; could not extract verbatim; Both emails decoded from Cloudflare cfemail attributes.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>South Central Ambulance Service NHS Foundation Trust</t>
+          <t>South Tyneside and Sunderland NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RYE</t>
+          <t>R0B</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>scas.oncallmedia@nhs.net</t>
+          <t>stsft.trustcomms@nhs.net</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>oncallmedia@scas.nhs.uk</t>
+          <t>lauren.robinson13@nhs.net</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://www.scas.nhs.uk/contact-us/contact-the-media-team/</t>
+          <t>https://www.stsft.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>scas.foi2@nhs.net</t>
+          <t>stsft.freedomofinformation@nhs.net</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>foi@scas.nhs.uk</t>
+          <t>stsft@infreemation.co.uk</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.scas.nhs.uk/contact-us/</t>
+          <t>https://www.stsft.nhs.uk/about-us/corporate-information/foi-requests</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>primary updated 2026-08-22 from https://www.scas.nhs.uk/contact-us/contact-the-media-team/ and https://www.scas.nhs.uk/contact-us/; prior values moved to _alt (press oncallmedia@scas.nhs.uk, foi foi@scas.nhs.uk) - the trust now publishes nhs.net team mailboxes on both pages</t>
+          <t>Trust uses third-party portal Stsft@infreemation.co.uk; nhs.net inbox is the auto-reply / fallback</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>South East Coast Ambulance Service NHS Foundation Trust</t>
+          <t>South Warwickshire University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RYD</t>
+          <t>RJC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>press@secamb.nhs.uk</t>
+          <t>communications@swft.nhs.uk</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://www.secamb.nhs.uk/news/contact-media-team/</t>
+          <t>https://www.swft.nhs.uk/about-us/contact-us</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>foi@secamb.nhs.uk</t>
+          <t>swft@infreemation.co.uk</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.secamb.nhs.uk/freedom-of-information-requests/</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>FOI email not located; South Warwickshire FOI sub-pages 404; contact page advises calling switchboard for FOI.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>South London and Maudsley NHS Foundation Trust</t>
+          <t>South West London and St George's Mental Health NHS Trust</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RV5</t>
+          <t>RQY</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>communications@slam.nhs.uk</t>
+          <t>communications@swlstg.nhs.uk</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://www.slam.nhs.uk/newsroom</t>
+          <t>https://www.swlstg.nhs.uk/media-enquiries</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>foi@slam.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>FOI-Requests@swlstg.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>foi@swlstg.nhs.uk</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.slam.nhs.uk/freedom-of-information</t>
+          <t>https://www.swlstg.nhs.uk/freedom-of-information</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -6250,237 +6246,237 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>South Tees Hospitals NHS Foundation Trust</t>
+          <t>South West Yorkshire Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RTR</t>
+          <t>RXG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>stees.public.relations@nhs.net</t>
+          <t>comms@swyt.nhs.uk</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://www.southtees.nhs.uk/press/</t>
+          <t>https://www.southwestyorkshire.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>stees.foi.admin@nhs.net</t>
+          <t>foi@swyt.nhs.uk</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.southtees.nhs.uk/freedom-of-information-foi/foi-contacts/</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Email addresses obscured by Cloudflare email-protection on both pages; could not extract verbatim; Both emails decoded from Cloudflare cfemail attributes.</t>
-        </is>
-      </c>
+          <t>https://www.southwestyorkshire.nhs.uk/contact-us/freedom-of-information/how-to-make-a-request/</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>South Tyneside and Sunderland NHS Foundation Trust</t>
+          <t>South Western Ambulance Service NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>R0B</t>
+          <t>RYF</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>stsft.trustcomms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>lauren.robinson13@nhs.net</t>
-        </is>
-      </c>
+          <t>publicrelations@swast.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.stsft.nhs.uk/contact-us</t>
+          <t>https://www.swast.nhs.uk/press-office</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>stsft.freedomofinformation@nhs.net</t>
+          <t>swast.information.governance@nhs.net</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>stsft@infreemation.co.uk</t>
+          <t>information.governance@swast.nhs.uk</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.stsft.nhs.uk/about-us/corporate-information/foi-requests</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Trust uses third-party portal Stsft@infreemation.co.uk; nhs.net inbox is the auto-reply / fallback</t>
-        </is>
-      </c>
+          <t>https://www.swast.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>South Warwickshire University NHS Foundation Trust</t>
+          <t>Hampshire and Isle of Wight Healthcare NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RJC</t>
+          <t>RW1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>communications@swft.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>hiowh.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>communications@southernhealth.nhs.uk</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.swft.nhs.uk/about-us/contact-us</t>
+          <t>https://hiowhealthcare.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>swft@infreemation.co.uk</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
+          <t>hiowh.freedomofinformation@nhs.net</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>freedom.information@southernhealth.nhs.uk</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://hiowhealthcare.nhs.uk/freedom-information</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>FOI email not located; South Warwickshire FOI sub-pages 404; contact page advises calling switchboard for FOI.</t>
+          <t>2026-08-22 ODS merge reconciliation: row R1C (Solent) retired and folded in; Solent and Southern Health merged 1 Oct 2024 to form Hampshire and Isle of Wight Healthcare NHS FT. Legacy Southern Health inboxes kept as _alt; legacy Solent inboxes were communications@solent.nhs.uk and FreedomOfInformation@solent.nhs.uk.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>South West London and St George's Mental Health NHS Trust</t>
+          <t>St George's University Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>RQY</t>
+          <t>RJ7</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>communications@swlstg.nhs.uk</t>
+          <t>gesh.comms@stgeorges.nhs.uk</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.swlstg.nhs.uk/media-enquiries</t>
+          <t>https://www.stgeorges.nhs.uk/news/media-enquiries/</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FOI-Requests@swlstg.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>foi@swlstg.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@stgeorges.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.swlstg.nhs.uk/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>FOI page lists postal address only; no email published; St George's FOI URL not fetched within budget.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>South West Yorkshire Partnership NHS Foundation Trust</t>
+          <t>Stockport NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RXG</t>
+          <t>RWJ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>comms@swyt.nhs.uk</t>
+          <t>communications@stockport.nhs.uk</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://www.southwestyorkshire.nhs.uk/contact-us/</t>
+          <t>https://www.stockport.nhs.uk/pressoffice/</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>foi@swyt.nhs.uk</t>
+          <t>foi@stockport.nhs.uk</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.southwestyorkshire.nhs.uk/contact-us/freedom-of-information/how-to-make-a-request/</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>https://www.stockport.nhs.uk/about/trust/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Contact page lists no media or FOI emails; FOI page not yet checked; Stockport FOI email decoded from Cloudflare cfemail. Contact-us page 404; no press email surfaced. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.stockport.nhs.uk/pressoffice/].</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>South Western Ambulance Service NHS Foundation Trust</t>
+          <t>Surrey and Borders Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RYF</t>
+          <t>RXX</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>publicrelations@swast.nhs.uk</t>
+          <t>communications@sabp.nhs.uk</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://www.swast.nhs.uk/press-office</t>
+          <t>https://www.sabp.nhs.uk/contact/media-enquiries</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>swast.information.governance@nhs.net</t>
+          <t>foi@sabp.nhs.uk</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>information.governance@swast.nhs.uk</t>
+          <t>igteam@sabp.nhs.uk</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.swast.nhs.uk/contact-us</t>
+          <t>https://www.sabp.nhs.uk/contact/freedom-of-info</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -6488,772 +6484,744 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Southern Health NHS Foundation Trust</t>
+          <t>Surrey and Sussex Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RW1</t>
+          <t>RTP</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>hiowh.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>communications@southernhealth.nhs.uk</t>
-        </is>
-      </c>
+          <t>sash.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://hiowhealthcare.nhs.uk/contact-us</t>
+          <t>https://www.surreyandsussex.nhs.uk/find-contact-us/contact-us/media-and-communications</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>hiowh.freedomofinformation@nhs.net</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>freedom.information@southernhealth.nhs.uk</t>
-        </is>
-      </c>
+          <t>sash.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://hiowhealthcare.nhs.uk/freedom-information</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Southern Health was reorganised into Hampshire and Isle of Wight Healthcare NHSFT</t>
-        </is>
-      </c>
+          <t>https://www.surreyandsussex.nhs.uk/about-us/corporate-and-regulatory-information/freedom-information/how-make-request</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>St George's University Hospitals NHS Foundation Trust</t>
+          <t>Sussex Community NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RJ7</t>
+          <t>RDR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>gesh.comms@stgeorges.nhs.uk</t>
+          <t>scftcommunications@nhs.net</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://www.stgeorges.nhs.uk/news/media-enquiries/</t>
+          <t>https://www.sussexcommunity.nhs.uk/contact-us/press-and-media</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>foi@stgeorges.nhs.uk</t>
+          <t>SC-TR.freedomofinformation@nhs.net</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.sussexcommunity.nhs.uk/contact-us/freedom-of-information</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>FOI page lists postal address only; no email published; St George's FOI URL not fetched within budget.</t>
+          <t>Both press and FOI pages returned 403 on direct fetch; emails are spam-obfuscated on the site. IG team based at Brighton General Hospital; Sussex Community: both press-and-media and FOI URLs returned 403 to WebFetch. | source URLs set 2026-06-06 via Playwright render; press scftcommunications@nhs.net and foi sc-tr.freedomofinformation@nhs.net both confirmed on-page (match primaries).</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Stockport NHS Foundation Trust</t>
+          <t>Sussex Partnership NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RWJ</t>
+          <t>RX2</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>communications@stockport.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>spft.media@nhs.net</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>communications@sussexpartnership.nhs.uk</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://www.stockport.nhs.uk/pressoffice/</t>
+          <t>https://www.sussexpartnership.nhs.uk/about-us/news-events</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>foi@stockport.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
+          <t>spft.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>foi@sussexpartnership.nhs.uk</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.stockport.nhs.uk/about/trust/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Contact page lists no media or FOI emails; FOI page not yet checked; Stockport FOI email decoded from Cloudflare cfemail. Contact-us page 404; no press email surfaced. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.stockport.nhs.uk/pressoffice/].</t>
-        </is>
-      </c>
+          <t>https://www.sussexpartnership.nhs.uk/about-us/contact-us/freedom-information</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Surrey and Borders Partnership NHS Foundation Trust</t>
+          <t>Tameside and Glossop Integrated Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RXX</t>
+          <t>RMP</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>communications@sabp.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>media@tgh.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>communication@tgh.nhs.uk</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.sabp.nhs.uk/contact/media-enquiries</t>
+          <t>https://www.tamesideandglossopicft.nhs.uk/contact-us/communicationpress</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>foi@sabp.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>igteam@sabp.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@tgh.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.sabp.nhs.uk/contact/freedom-of-info</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>https://www.tamesideandglossopicft.nhs.uk/about-us/freedom-information-foi/freedom-information-request</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>press/comms page not located</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Surrey and Sussex Healthcare NHS Trust</t>
+          <t>Tees, Esk and Wear Valleys NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RTP</t>
+          <t>RX3</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>sash.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>tewv.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>tewv.enquiries@nhs.net</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.surreyandsussex.nhs.uk/find-contact-us/contact-us/media-and-communications</t>
+          <t>https://www.tewv.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>sash.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
+          <t>TEAWVNT.accessrequests@nhs.net</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>tewv.foi@nhs.net</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.surreyandsussex.nhs.uk/about-us/corporate-and-regulatory-information/freedom-information/how-make-request</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>https://www.tewv.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>FOI handled via Access Requests inbox per contact page; Cloudflare email-protection decoded</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sussex Community NHS Foundation Trust</t>
+          <t>The Christie NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RDR</t>
+          <t>RBV</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>scftcommunications@nhs.net</t>
+          <t>Maggie.Doyle@christie.nhs.uk</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.sussexcommunity.nhs.uk/contact-us/press-and-media</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SC-TR.freedomofinformation@nhs.net</t>
+          <t>the-christie.foi@nhs.net</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.sussexcommunity.nhs.uk/contact-us/freedom-of-information</t>
+          <t>https://www.christie.nhs.uk/about-us/about-the-christie/freedom-of-information-disclosure-logs</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Both press and FOI pages returned 403 on direct fetch; emails are spam-obfuscated on the site. IG team based at Brighton General Hospital; Sussex Community: both press-and-media and FOI URLs returned 403 to WebFetch. | source URLs set 2026-06-06 via Playwright render; press scftcommunications@nhs.net and foi sc-tr.freedomofinformation@nhs.net both confirmed on-page (match primaries).</t>
+          <t>Press/media email not surfaced on contact-us page; Christie communications switchboard 0161 446 3000; Christie press office sub-pages all 404 in tests; no press email surfaced.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sussex Partnership NHS Foundation Trust</t>
+          <t>The Clatterbridge Cancer Centre NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>RX2</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>spft.media@nhs.net</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>communications@sussexpartnership.nhs.uk</t>
-        </is>
-      </c>
+          <t>ccf-tr.communications.team@nhs.net</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.sussexpartnership.nhs.uk/about-us/news-events</t>
+          <t>https://www.clatterbridgecc.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>spft.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>foi@sussexpartnership.nhs.uk</t>
-        </is>
-      </c>
+          <t>ccf-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.sussexpartnership.nhs.uk/about-us/contact-us/freedom-information</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>https://www.clatterbridgecc.nhs.uk/about-us/freedom-information-foi</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>site returned 403 to bot fetch; pages exist per search results, but specific email addresses could not be confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Tameside and Glossop Integrated Care NHS Foundation Trust</t>
+          <t>The Dudley Group NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RMP</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>media@tgh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>communication@tgh.nhs.uk</t>
-        </is>
-      </c>
+          <t>dgft.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.tamesideandglossopicft.nhs.uk/contact-us/communicationpress</t>
+          <t>https://www.dgft.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>foi@tgh.nhs.uk</t>
+          <t>dgft.foi@nhs.net</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.tamesideandglossopicft.nhs.uk/about-us/freedom-information-foi/freedom-information-request</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>press/comms page not located</t>
-        </is>
-      </c>
+          <t>https://www.dgft.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tavistock and Portman NHS Foundation Trust</t>
+          <t>The Hillingdon Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RNK</t>
+          <t>RAS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>nlft.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>media@tavi-port.nhs.uk</t>
-        </is>
-      </c>
+          <t>thh-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
+          <t>https://thh.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>nlft.freedom.information@nhs.net</t>
+          <t>thh@infreemation.co.uk</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>foi@tavi-port.nhs.uk</t>
+          <t>thh-tr.freedomofinfo@nhs.net</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
+          <t>https://thh.nhs.uk/freedom-of-information/</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Trust merged into North London FT April 2026; archived site; Note: Tavistock &amp; Portman merged into North London NHS FT on 1 April 2026 - site archived. 2026-08-15: tavistockandportman.nhs.uk now 301-redirects to northlondonmentalhealth.nhs.uk (North London NHS Foundation Trust); both prior source URLs are dead. press + foi primaries updated from [https://www.northlondonmentalhealth.nhs.uk/contact-us]; prior values moved to _alt (displaced prior press _alt was communications@tavi-port.nhs.uk).</t>
+          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026. 2026-07-04: FOI source URL refreshed (old /about-us/ page 404); still online-form only (thh.disclosure-log.co.uk), no email published.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tees, Esk and Wear Valleys NHS Foundation Trust</t>
+          <t>The Newcastle upon Tyne Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RX3</t>
+          <t>RTD</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>tewv.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>tewv.enquiries@nhs.net</t>
-        </is>
-      </c>
+          <t>nuth.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.tewv.nhs.uk/contact/</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>TEAWVNT.accessrequests@nhs.net</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>tewv.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>https://www.newcastle-hospitals.nhs.uk/help/press/</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.tewv.nhs.uk/freedom-of-information/</t>
+          <t>https://www.newcastle-hospitals.nhs.uk/help/foi/</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>FOI handled via Access Requests inbox per contact page; Cloudflare email-protection decoded</t>
+          <t>Newcastle press email inferred from Bing cross-reference (Cloudflare-encoded on page); FOI page directs requests via online form, no email. FOI source URL recorded 2026-07-30: /help/foi/ re-checked and still publishes no FOI mailbox - requests go through an on-page web form only, so foi_email stays null.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>The Christie NHS Foundation Trust</t>
+          <t>The Princess Alexandra Hospital NHS Trust</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RBV</t>
+          <t>RQW</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Maggie.Doyle@christie.nhs.uk</t>
+          <t>paht.communications@nhs.net</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://www.pah.nhs.uk/contact/media-enquiries/</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>the-christie.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr"/>
+          <t>paht.FOI@nhs.net</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>FOI@pah.nhs.uk</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.christie.nhs.uk/about-us/about-the-christie/freedom-of-information-disclosure-logs</t>
+          <t>https://www.pah.nhs.uk/foi/request/</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Press/media email not surfaced on contact-us page; Christie communications switchboard 0161 446 3000; Christie press office sub-pages all 404 in tests; no press email surfaced.</t>
+          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified. | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged | 2026-08-22: foi_source_url repointed from the spreadsheet placeholder to the live /foi/request/ page (online form only, no address published there); FOI@pah.nhs.uk recorded as _alt from the trust's own FOI guidance. Press address paht.communications@nhs.net re-confirmed by decoding the cfemail token on the media-enquiries page.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>The Clatterbridge Cancer Centre NHS Foundation Trust</t>
+          <t>The Queen Elizabeth Hospital King's Lynn NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RCX</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ccf-tr.communications.team@nhs.net</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>media.enquiries@qehkl.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Communicationsqeh@qehkl.nhs.uk</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.clatterbridgecc.nhs.uk/contact-us</t>
+          <t>https://www.qehkl.nhs.uk/about-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>ccf-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>dpa@qehkl.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>foi@qehkl.nhs.uk</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.clatterbridgecc.nhs.uk/about-us/freedom-information-foi</t>
+          <t>https://www.qehkl.nhs.uk/freedom-of-information.asp</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>site returned 403 to bot fetch; pages exist per search results, but specific email addresses could not be confirmed</t>
+          <t>FOI uses combined data protection / FOI inbox press source URL updated 2026-07-30: /news-and-events/media-enquiries/ now 404s, page moved to /about-us/media-enquiries/; media.enquiries@qehkl.nhs.uk confirmed there, address unchanged. Note the FOI page designates foi@qehkl.nhs.uk (currently held in _alt) while dpa@ is the data-protection inbox.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>The Dudley Group NHS Foundation Trust</t>
+          <t>The Robert Jones and Agnes Hunt Orthopaedic Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RNA</t>
+          <t>RL1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>dgft.communications@nhs.net</t>
+          <t>rjah.media.requests@nhs.net</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.dgft.nhs.uk/contact-us/</t>
+          <t>https://www.rjah.nhs.uk/contact-us/media-enquiries/</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>dgft.foi@nhs.net</t>
+          <t>rjah.foi@nhs.net</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.dgft.nhs.uk/about-us/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>https://www.rjah.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. Trust asks media to route all enquiries via the press office rather than contacting staff directly.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>The Hillingdon Hospitals NHS Foundation Trust</t>
+          <t>The Rotherham NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RAS</t>
+          <t>RFR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>thh-tr.communications@nhs.net</t>
+          <t>rgh-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://thh.nhs.uk/contact-us/</t>
+          <t>https://www.therotherhamft.nhs.uk/contact/media-enquiries</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>thh@infreemation.co.uk</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>thh-tr.freedomofinfo@nhs.net</t>
-        </is>
-      </c>
+          <t>rgh-tr.freedomofinformation@nhs.net</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://thh.nhs.uk/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Trust directs FOI requests to online form at thh.disclosure-log.co.uk; no published email; Hillingdon Hospitals FOI page directs all requests via online form (thh.disclosure-log.co.uk); states attachments and links rejected; no FOI email published.; Hillingdon use the Infreemation portal — confirmed via WhatDoTheyKnow request thread, May 2026. 2026-07-04: FOI source URL refreshed (old /about-us/ page 404); still online-form only (thh.disclosure-log.co.uk), no email published.</t>
-        </is>
-      </c>
+          <t>https://www.therotherhamft.nhs.uk/contact/freedom-information</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>The Newcastle upon Tyne Hospitals NHS Foundation Trust</t>
+          <t>The Royal Marsden NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RTD</t>
+          <t>RPY</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>nuth.communications@nhs.net</t>
+          <t>pressteam@rmh.nhs.uk</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.newcastle-hospitals.nhs.uk/help/press/</t>
+          <t>https://www.royalmarsden.nhs.uk/contact-us/pr-and-communications-team</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.newcastle-hospitals.nhs.uk/help/foi/</t>
+          <t>https://www.royalmarsden.nhs.uk/about-royal-marsden/freedom-information</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Newcastle press email inferred from Bing cross-reference (Cloudflare-encoded on page); FOI page directs requests via online form, no email. FOI source URL recorded 2026-07-30: /help/foi/ re-checked and still publishes no FOI mailbox - requests go through an on-page web form only, so foi_email stays null.</t>
+          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget. | 2026-06-20: Royal Marsden publishes no FOI email address (online form only) | 2026-08-22: pressteam@rmh.nhs.uk re-confirmed; FOI page still publishes no address (online form only), so foi_email stays null.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>The Princess Alexandra Hospital NHS Trust</t>
+          <t>The Royal Orthopaedic Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RQW</t>
+          <t>RRJ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>paht.communications@nhs.net</t>
+          <t>roh.comms@nhs.net</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://www.pah.nhs.uk/contact/media-enquiries/</t>
+          <t>https://roh.nhs.uk/contact</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>paht.FOI@nhs.net</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>FOI@pah.nhs.uk</t>
-        </is>
-      </c>
+          <t>roh-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.pah.nhs.uk/foi/request/</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>PAH uses online forms only for both media and FOI; emails are CloudFlare-protected share links not contact addresses; no direct inbox visible; Princess Alexandra: media page provides only enquiry form; FOI page Cloudflare-protected (cfemail not extracted). pah.foi@nhs.net is plausible but unverified. | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged | 2026-08-22: foi_source_url repointed from the spreadsheet placeholder to the live /foi/request/ page (online form only, no address published there); FOI@pah.nhs.uk recorded as _alt from the trust's own FOI guidance. Press address paht.communications@nhs.net re-confirmed by decoding the cfemail token on the media-enquiries page.</t>
-        </is>
-      </c>
+          <t>https://roh.nhs.uk/contact</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>The Queen Elizabeth Hospital King's Lynn NHS Foundation Trust</t>
+          <t>The Royal Wolverhampton NHS Trust</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RCX</t>
+          <t>RL4</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>media.enquiries@qehkl.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Communicationsqeh@qehkl.nhs.uk</t>
-        </is>
-      </c>
+          <t>rwh-tr.communicationsdept@nhs.net</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://www.qehkl.nhs.uk/about-us/media-enquiries/</t>
+          <t>https://www.royalwolverhampton.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>dpa@qehkl.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>foi@qehkl.nhs.uk</t>
-        </is>
-      </c>
+          <t>rwh-tr.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.qehkl.nhs.uk/freedom-of-information.asp</t>
+          <t>https://www.royalwolverhampton.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>FOI uses combined data protection / FOI inbox press source URL updated 2026-07-30: /news-and-events/media-enquiries/ now 404s, page moved to /about-us/media-enquiries/; media.enquiries@qehkl.nhs.uk confirmed there, address unchanged. Note the FOI page designates foi@qehkl.nhs.uk (currently held in _alt) while dpa@ is the data-protection inbox.</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page. Press address is listed there as 'Website Enquiries / Media / Press', so it is not media-only.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>The Robert Jones and Agnes Hunt Orthopaedic Hospital NHS Foundation Trust</t>
+          <t>The Shrewsbury and Telford Hospital NHS Trust</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RL1</t>
+          <t>RXW</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>rjah.media.requests@nhs.net</t>
+          <t>sath.commsteam@nhs.net</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://www.rjah.nhs.uk/contact-us/media-enquiries/</t>
+          <t>https://www.sath.nhs.uk/news-media/contact-the-team/</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>rjah.foi@nhs.net</t>
+          <t>sath.foi@nhs.net</t>
         </is>
       </c>
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.rjah.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. Trust asks media to route all enquiries via the press office rather than contacting staff directly.</t>
-        </is>
-      </c>
+          <t>https://www.sath.nhs.uk/about-us/freedom-of-information/make-an-enquiry/</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>The Rotherham NHS Foundation Trust</t>
+          <t>The Walton Centre NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RFR</t>
+          <t>RET</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>rgh-tr.communications@nhs.net</t>
+          <t>wcft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://www.therotherhamft.nhs.uk/contact/media-enquiries</t>
+          <t>https://www.thewaltoncentre.nhs.uk/media-enquiries</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>rgh-tr.freedomofinformation@nhs.net</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr"/>
+          <t>wcft.enquiries@nhs.net</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>enquiries@thewaltoncentre.nhs.uk</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.therotherhamft.nhs.uk/contact/freedom-information</t>
+          <t>https://www.thewaltoncentre.nhs.uk/freedom-of-information-requests---form</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -7261,432 +7229,452 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>The Royal Marsden NHS Foundation Trust</t>
+          <t>Torbay and South Devon NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>RPY</t>
+          <t>RA9</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>pressteam@rmh.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>tsdft.communicationsteam@nhs.net</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>communications.tsdft@nhs.net</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://www.royalmarsden.nhs.uk/contact-us/pr-and-communications-team</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+          <t>https://www.torbayandsouthdevon.nhs.uk/about-us/news-and-publications/media-relations/</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>tsdft.foirequests@nhs.net</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>foi.tsdft@nhs.net</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.royalmarsden.nhs.uk/about-royal-marsden/freedom-information</t>
+          <t>https://www.torbayandsouthdevon.nhs.uk/about-us/data-protection/freedom-of-information/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Royal Marsden FOI handled via online request form only; no public FOI inbox; Royal Marsden FOI URL not fetched within budget. | 2026-06-20: Royal Marsden publishes no FOI email address (online form only) | 2026-08-22: pressteam@rmh.nhs.uk re-confirmed; FOI page still publishes no address (online form only), so foi_email stays null.</t>
+          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net) | press source URL corrected 2026-06-20 (prior URL 404); address unchanged | 2026-08-22: media-relations page is contact-form only with no address published, so the reconstructed press address is retained unverified; tsdft.foirequests@nhs.net re-confirmed.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>The Royal Orthopaedic Hospital NHS Foundation Trust</t>
+          <t>United Lincolnshire Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RRJ</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>roh.comms@nhs.net</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>ulth.lchscommunications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>communications@ulh.nhs.uk</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://roh.nhs.uk/contact</t>
+          <t>https://www.ulh.nhs.uk/contact/news-communications/</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>roh-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
+          <t>ulth.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>FOI@ulh.nhs.uk</t>
+        </is>
+      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://roh.nhs.uk/contact</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>https://www.ulh.nhs.uk/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Both emails obscured by Cloudflare email-protection on these pages</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>The Royal Wolverhampton NHS Trust</t>
+          <t>University College London Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RL4</t>
+          <t>RRV</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>rwh-tr.communicationsdept@nhs.net</t>
+          <t>uclh.media@nhs.net</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://www.royalwolverhampton.nhs.uk/contact-us/</t>
+          <t>https://www.uclh.nhs.uk/about-us/what-we-do/media-and-communications/media-enquiries/story-consent</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>rwh-tr.foi@nhs.net</t>
+          <t>uclh.foi@nhs.net</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.royalwolverhampton.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>2026-08-18: press and FOI emails both re-verified against the trust's own contact-us page. Press address is listed there as 'Website Enquiries / Media / Press', so it is not media-only.</t>
-        </is>
-      </c>
+          <t>https://www.uclh.nhs.uk/contact/freedom-information</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>The Shrewsbury and Telford Hospital NHS Trust</t>
+          <t>University Hospital Southampton NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RXW</t>
+          <t>RHM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>sath.commsteam@nhs.net</t>
+          <t>communications@uhs.nhs.uk</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://www.sath.nhs.uk/news-media/contact-the-team/</t>
+          <t>https://www.uhs.nhs.uk/whats-new/procedure-for-media-enquiries</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>sath.foi@nhs.net</t>
+          <t>freedomofinformation@uhs.nhs.uk</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.sath.nhs.uk/about-us/freedom-of-information/make-an-enquiry/</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>https://www.uhs.nhs.uk/about-the-trust/privacy/requesting-information-about-university-hospital-southampton</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Trust website returned 404 to direct page fetches; FOI email not confirmed; UH Southampton FOI sub-pages all 404 across tested paths.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>The Walton Centre NHS Foundation Trust</t>
+          <t>University Hospitals Birmingham NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>RET</t>
+          <t>RRK</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>wcft.communications@nhs.net</t>
+          <t>communications@uhb.nhs.uk</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://www.thewaltoncentre.nhs.uk/media-enquiries</t>
+          <t>https://www.uhb.nhs.uk/get-in-touch/media-enquiries/</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>wcft.enquiries@nhs.net</t>
+          <t>Foi@uhb.nhs.uk</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>enquiries@thewaltoncentre.nhs.uk</t>
+          <t>foi.uhb@uhb.nhs.uk</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.thewaltoncentre.nhs.uk/freedom-of-information-requests---form</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>https://www.uhb.nhs.uk/get-in-touch/make-a-freedom-of-information-request/</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>press email not found on site; FOI email not found on site | 2026-08-22: both addresses now confirmed on the trust's own pages (communications@uhb.nhs.uk on /get-in-touch/media-enquiries/, Foi@uhb.nhs.uk on /get-in-touch/make-a-freedom-of-information-request/) - the earlier 'not found on site' note is superseded.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Torbay and South Devon NHS Foundation Trust</t>
+          <t>Bristol NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RA9</t>
+          <t>RA7</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>tsdft.communicationsteam@nhs.net</t>
+          <t>pressoffice@uhbw.nhs.uk</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>communications.tsdft@nhs.net</t>
+          <t>nbtcommunications@nbt.nhs.uk</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://www.torbayandsouthdevon.nhs.uk/about-us/news-and-publications/media-relations/</t>
+          <t>https://www.bristolft.nhs.uk/about-us/news-and-media/media-enquiries</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>tsdft.foirequests@nhs.net</t>
+          <t>FreedomOfInfo@uhbw.nhs.uk</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>foi.tsdft@nhs.net</t>
+          <t>FOIArequests@nbt.nhs.uk</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.torbayandsouthdevon.nhs.uk/about-us/data-protection/freedom-of-information/</t>
+          <t>https://www.bristolft.nhs.uk/contact-us/freedom-information</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Press email reconstructed from contact form recipient (tsdft.communicationsteam@nhs.net) | press source URL corrected 2026-06-20 (prior URL 404); address unchanged | 2026-08-22: media-relations page is contact-form only with no address published, so the reconstructed press address is retained unverified; tsdft.foirequests@nhs.net re-confirmed.</t>
+          <t>2026-08-22 ODS merge reconciliation: row RVJ (North Bristol) retired and folded in; merged 1 Jul 2026 to form Bristol NHS FT. The trust still runs two site-based routes and publishes no single trust-wide address. Press: city centre / South Bristol / Weston is phone-only on its own page (0117 342 3629; out of hours switchboard 0117 923 0000, ask for the on-call press officer) but pressoffice@uhbw.nhs.uk is still live on the UHBW media centre; Southmead / Cossham / Bristol Centre for Enablement is nbtcommunications@nbt.nhs.uk (0117 414 3990). FOI: City and Weston by email to FreedomOfInfo@uhbw.nhs.uk; Southmead via a web form at https://nhs1.radarhealthcare.net/incident/27/external-form/NBNT/Template_NHS_FOI_Request/694 with FOIArequests@nbt.nhs.uk still published on nbt.nhs.uk.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>United Lincolnshire Hospitals NHS Trust</t>
+          <t>University Hospitals Coventry and Warwickshire NHS Trust</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RWD</t>
+          <t>RKB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ulth.lchscommunications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>communications@ulh.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications@uhcw.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://www.ulh.nhs.uk/contact/news-communications/</t>
+          <t>https://www.uhcw.nhs.uk/contact-us/media-centre/media-enquiries/</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>ulth.foi@nhs.net</t>
+          <t>GMBFOI@uhcw.nhs.uk</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FOI@ulh.nhs.uk</t>
+          <t>foi@uhcw.nhs.uk</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.ulh.nhs.uk/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Both emails obscured by Cloudflare email-protection on these pages</t>
-        </is>
-      </c>
+          <t>https://www.uhcw.nhs.uk/contact-us/freedom-of-information-act/</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>University College London Hospitals NHS Foundation Trust</t>
+          <t>University Hospitals Dorset NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>RRV</t>
+          <t>R0D</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>uclh.media@nhs.net</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>uhd.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>communications@uhd.nhs.uk</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://www.uclh.nhs.uk/about-us/what-we-do/media-and-communications/media-enquiries/story-consent</t>
+          <t>https://www.uhd.nhs.uk/news/media-enquiry</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>uclh.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr"/>
+          <t>uhd.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>foi@uhd.nhs.uk</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.uclh.nhs.uk/contact/freedom-information</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
+          <t>https://www.uhd.nhs.uk/about-us/foi</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Joomla cloak-script obfuscated; decoded from script source</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>University Hospital Southampton NHS Foundation Trust</t>
+          <t>University Hospitals Plymouth NHS Trust</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RHM</t>
+          <t>RK9</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>communications@uhs.nhs.uk</t>
+          <t>communications.phnt@nhs.net</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://www.uhs.nhs.uk/whats-new/procedure-for-media-enquiries</t>
+          <t>https://www.plymouthhospitals.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>freedomofinformation@uhs.nhs.uk</t>
+          <t>plh-tr.foi-requests@nhs.net</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.uhs.nhs.uk/about-the-trust/privacy/requesting-information-about-university-hospital-southampton</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Trust website returned 404 to direct page fetches; FOI email not confirmed; UH Southampton FOI sub-pages all 404 across tested paths.</t>
-        </is>
-      </c>
+          <t>https://www.plymouthhospitals.nhs.uk/foi/</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>University Hospitals Birmingham NHS Foundation Trust</t>
+          <t>University Hospitals Sussex NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RRK</t>
+          <t>RYR</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>communications@uhb.nhs.uk</t>
+          <t>UHSussex.media@nhs.net</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://www.uhb.nhs.uk/get-in-touch/media-enquiries/</t>
+          <t>https://www.uhsussex.nhs.uk/contact/press-media/</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Foi@uhb.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>foi.uhb@uhb.nhs.uk</t>
-        </is>
-      </c>
+          <t>UHSussex.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.uhb.nhs.uk/get-in-touch/make-a-freedom-of-information-request/</t>
+          <t>https://www.uhsussex.nhs.uk/freedom-of-information/</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site | 2026-08-22: both addresses now confirmed on the trust's own pages (communications@uhb.nhs.uk on /get-in-touch/media-enquiries/, Foi@uhb.nhs.uk on /get-in-touch/make-a-freedom-of-information-request/) - the earlier 'not found on site' note is superseded.</t>
+          <t>Cloudflare email-protection decoded</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>University Hospitals Bristol and Weston NHS Foundation Trust</t>
+          <t>University Hospitals of Derby and Burton NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RA7</t>
+          <t>RTG</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>pressoffice@uhbw.nhs.uk</t>
+          <t>uhdb.communications@nhs.net</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://www.uhbw.nhs.uk/p/get-in-touch/media-centre</t>
+          <t>https://www.uhdb.nhs.uk/information-for-journalists</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FreedomOfInfo@uhbw.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>FreedomofInfo@uhbristol.nhs.uk</t>
-        </is>
-      </c>
+          <t>uhdb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.uhbw.nhs.uk/p/how-we-use-your-data/freedom-of-information-foi-requests</t>
+          <t>https://www.uhdb.nhs.uk/freedom-of-information-foi</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -7694,120 +7682,120 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>University Hospitals Coventry and Warwickshire NHS Trust</t>
+          <t>University Hospitals of Leicester NHS Trust</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RKB</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>communications@uhcw.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>uhl-tr.pressoffice@nhs.net</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>communications@uhl-tr.nhs.uk</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://www.uhcw.nhs.uk/contact-us/media-centre/media-enquiries/</t>
+          <t>https://www.uhleicester.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>GMBFOI@uhcw.nhs.uk</t>
+          <t>uhl-tr.foi-freedomofinformation@nhs.net</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>foi@uhcw.nhs.uk</t>
+          <t>foi@uhl-tr.nhs.uk</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.uhcw.nhs.uk/contact-us/freedom-of-information-act/</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>https://www.uhleicester.nhs.uk/foi/about-freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Press email obscured/encoded on contact page; FOI page not located</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>University Hospitals Dorset NHS Foundation Trust</t>
+          <t>University Hospitals of Morecambe Bay NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>R0D</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>uhd.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>communications@uhd.nhs.uk</t>
-        </is>
-      </c>
+          <t>communications.team@mbht.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://www.uhd.nhs.uk/news/media-enquiry</t>
+          <t>https://www.uhmb.nhs.uk/get-in-touch/contact-our-corporate-communications-team</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>uhd.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>foi@uhd.nhs.uk</t>
-        </is>
-      </c>
+          <t>Freedom.Information@mbht.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.uhd.nhs.uk/about-us/foi</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Joomla cloak-script obfuscated; decoded from script source</t>
-        </is>
-      </c>
+          <t>https://www.uhmb.nhs.uk/our-trust/freedom-information</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>University Hospitals Plymouth NHS Trust</t>
+          <t>University Hospitals of North Midlands NHS Trust</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RK9</t>
+          <t>RJE</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>communications.phnt@nhs.net</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>communications@uhnm.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Communications@uh​nm.n​hs.uk</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://www.plymouthhospitals.nhs.uk/contact-us</t>
+          <t>https://www.uhnm.nhs.uk/contact-us/information-for-journalists/</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>plh-tr.foi-requests@nhs.net</t>
+          <t>foi@uhnm.nhs.uk</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.plymouthhospitals.nhs.uk/foi/</t>
+          <t>https://www.uhnm.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -7815,155 +7803,167 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>University Hospitals Sussex NHS Foundation Trust</t>
+          <t>Walsall Healthcare NHS Trust</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RYR</t>
+          <t>RBK</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>UHSussex.media@nhs.net</t>
+          <t>wht.communications@nhs.net</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://www.uhsussex.nhs.uk/contact/press-media/</t>
+          <t>Temp/Comms contacts.xlsx (May 2026)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>UHSussex.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
+          <t>wht.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>FOI@walsallhealthcare.nhs.uk</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.uhsussex.nhs.uk/freedom-of-information/</t>
+          <t>https://www.walsallhealthcare.nhs.uk/about-us/foi/</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Cloudflare email-protection decoded</t>
+          <t>No press email published; out-of-hours via switchboard 01922 721172; Walsall Healthcare media page advises out-of-hours via switchboard only; no published press email.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>University Hospitals of Derby and Burton NHS Foundation Trust</t>
+          <t>North Cheshire and Mersey NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RTG</t>
+          <t>RWW</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>uhdb.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>ncm.media@nhs.net</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>whh.communications@nhs.net</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://www.uhdb.nhs.uk/information-for-journalists</t>
+          <t>https://northcheshireandmersey.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>uhdb.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
+          <t>ncm.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>whh.foi@nhs.net</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.uhdb.nhs.uk/freedom-of-information-foi</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-08-22 ODS merge reconciliation: row RY2 (Bridgewater Community Healthcare) retired and folded in; Bridgewater and Warrington and Halton Teaching Hospitals merged 1 Apr 2026 to form North Cheshire and Mersey NHS FT, which uses shared ncm.* inboxes. Legacy WHH inboxes kept as _alt; legacy Bridgewater FOI inbox was foi@bridgewater.nhs.uk.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>University Hospitals of Leicester NHS Trust</t>
+          <t>West Hertfordshire Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>RWG</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>uhl-tr.pressoffice@nhs.net</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>communications@uhl-tr.nhs.uk</t>
-        </is>
-      </c>
+          <t>westherts.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://www.uhleicester.nhs.uk/contact/</t>
+          <t>https://www.westhertshospitals.nhs.uk/about-us/news/media-enquiries</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>uhl-tr.foi-freedomofinformation@nhs.net</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>foi@uhl-tr.nhs.uk</t>
-        </is>
-      </c>
+          <t>westherts.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.uhleicester.nhs.uk/foi/about-freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Press email obscured/encoded on contact page; FOI page not located</t>
-        </is>
-      </c>
+          <t>https://www.westhertshospitals.nhs.uk/about-us/foi</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>University Hospitals of Morecambe Bay NHS Foundation Trust</t>
+          <t>West London NHS Trust</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>RKL</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>communications.team@mbht.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>wlt.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>communications@westlondon.nhs.uk</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://www.uhmb.nhs.uk/get-in-touch/contact-our-corporate-communications-team</t>
+          <t>https://www.westlondon.nhs.uk/news/media-and-communications</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Freedom.Information@mbht.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr"/>
+          <t>wlt.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>foi@westlondon.nhs.uk</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.uhmb.nhs.uk/our-trust/freedom-information</t>
+          <t>https://www.westlondon.nhs.uk/about-us/freedom-information</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -7971,280 +7971,260 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>University Hospitals of North Midlands NHS Trust</t>
+          <t>West Midlands Ambulance Service University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RJE</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>communications@uhnm.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Communications@uh​nm.n​hs.uk</t>
-        </is>
-      </c>
+          <t>pressoffice@wmas.nhs.uk</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://www.uhnm.nhs.uk/contact-us/information-for-journalists/</t>
+          <t>https://www.wmas.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>foi@uhnm.nhs.uk</t>
+          <t>foi@wmas.nhs.uk</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.uhnm.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>https://www.wmas.nhs.uk/foi/</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Cloudflare email-protection decoded</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Walsall Healthcare NHS Trust</t>
+          <t>West Suffolk NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RBK</t>
+          <t>RGR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>wht.communications@nhs.net</t>
+          <t>media@wsh.nhs.uk</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>http://www.wsh.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>wht.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>FOI@walsallhealthcare.nhs.uk</t>
-        </is>
-      </c>
+          <t>foi@wsh.nhs.uk</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.walsallhealthcare.nhs.uk/about-us/foi/</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>No press email published; out-of-hours via switchboard 01922 721172; Walsall Healthcare media page advises out-of-hours via switchboard only; no published press email.</t>
-        </is>
-      </c>
+          <t>http://www.wsh.nhs.uk/contact-us/</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Warrington and Halton Teaching Hospitals NHS Foundation Trust</t>
+          <t>Whittington Health NHS Trust</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RWW</t>
+          <t>RKE</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ncm.media@nhs.net</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>whh.communications@nhs.net</t>
-        </is>
-      </c>
+          <t>communications.whitthealth@nhs.net</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://northcheshireandmersey.nhs.uk/contact-us</t>
+          <t>https://www.whittington.nhs.uk/default.asp?c=23363</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>ncm.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>whh.foi@nhs.net</t>
-        </is>
-      </c>
+          <t>foi.whitthealth@nhs.net</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/</t>
+          <t>https://www.whittington.nhs.uk/default.asp?c=1631</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>FOI primary updated 2026-05-16 from https://northcheshireandmersey.nhs.uk/about-us/freedom-of-information/; prior value moved to _alt</t>
+          <t>FOI email not located; Whittington FOI sub-pages (default.asp ?c= numeric IDs) all 404 in tests. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.whittington.nhs.uk/default.asp?c=1631].</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>West Hertfordshire Teaching Hospitals NHS Trust</t>
+          <t>Wirral Community Health and Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RWG</t>
+          <t>RY7</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>westherts.communications@nhs.net</t>
+          <t>wcnt.communications@nhs.net</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://www.westhertshospitals.nhs.uk/about-us/news/media-enquiries</t>
+          <t>https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>westherts.foi@nhs.net</t>
+          <t>wcnt.foi@nhs.net</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.westhertshospitals.nhs.uk/about-us/foi</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>https://www.wchc.nhs.uk/about/freedom-information/act/</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>no listed emails on either page; phone-only contact; Wirral Community: contact page lists media phone numbers but no email; FOI page lists no email; sub-paths 404. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/]. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/freedom-information/act/].</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>West London NHS Trust</t>
+          <t>Wirral University Teaching Hospital NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RKL</t>
+          <t>RBL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>wlt.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>communications@westlondon.nhs.uk</t>
-        </is>
-      </c>
+          <t>wih-tr.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://www.westlondon.nhs.uk/news/media-and-communications</t>
+          <t>https://www.wuth.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>wlt.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>foi@westlondon.nhs.uk</t>
-        </is>
-      </c>
+          <t>wih-tr.accesstoinformationoffice@nhs.net</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.westlondon.nhs.uk/about-us/freedom-information</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>https://www.wuth.nhs.uk/contact-us</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>FOI inbox combined with Access to Information Office (handles both FOI and SARs)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>West Midlands Ambulance Service University NHS Foundation Trust</t>
+          <t>Worcestershire Acute Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>RWP</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>pressoffice@wmas.nhs.uk</t>
+          <t>wah-tr.communications@nhs.net</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://www.wmas.nhs.uk/contact/</t>
+          <t>https://www.worcsacute.nhs.uk/contact-us/press-office/</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>foi@wmas.nhs.uk</t>
+          <t>wah-tr.foi@nhs.net</t>
         </is>
       </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.wmas.nhs.uk/foi/</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Cloudflare email-protection decoded</t>
-        </is>
-      </c>
+          <t>https://www.worcsacute.nhs.uk/our-trust/freedom-of-information/freedom-of-information-publication-scheme/</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>West Suffolk NHS Foundation Trust</t>
+          <t>Wrightington, Wigan and Leigh Teaching Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RGR</t>
+          <t>RRF</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>media@wsh.nhs.uk</t>
+          <t>PRenquiries@wwl.nhs.uk</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>http://www.wsh.nhs.uk/contact-us/</t>
+          <t>https://www.wwl.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>foi@wsh.nhs.uk</t>
+          <t>FOI@wwl.nhs.uk</t>
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>http://www.wsh.nhs.uk/contact-us/</t>
+          <t>https://www.wwl.nhs.uk/freedom-of-information</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -8252,360 +8232,173 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Whittington Health NHS Trust</t>
+          <t>Wye Valley NHS Trust</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RKE</t>
+          <t>RLQ</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>communications.whitthealth@nhs.net</t>
+          <t>WVTcommsteam@wvt.nhs.uk</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://www.whittington.nhs.uk/default.asp?c=23363</t>
+          <t>https://www.wyevalley.nhs.uk/news-events/press-office.aspx</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>foi.whitthealth@nhs.net</t>
+          <t>Freedom.Information@wvt.nhs.uk</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.whittington.nhs.uk/default.asp?c=1631</t>
+          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>FOI email not located; Whittington FOI sub-pages (default.asp ?c= numeric IDs) all 404 in tests. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.whittington.nhs.uk/default.asp?c=1631].</t>
+          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. foi_source_url repointed - the old freedom-of-information-requests.aspx now 404s. Press office page also lists three named comms staff (John Burnett, comms and engagement manager; Amanda Millichip and Fiona Gurney, comms officers) on 01432 372928. | 2026-08-22: foi_source_url repointed again - make-a-freedom-of-information-request.aspx now 404s; Freedom.Information@wvt.nhs.uk is published on the parent /about-us/information-requests/ page. Press address re-confirmed on the press office page.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Wirral Community Health and Care NHS Foundation Trust</t>
+          <t>York and Scarborough Teaching Hospitals NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RY7</t>
+          <t>RCB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>wcnt.communications@nhs.net</t>
+          <t>yhs-tr.communications.team@nhs.net</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/</t>
+          <t>https://www.yorkhospitals.nhs.uk/news-amp-media/media-enquiries/</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>wcnt.foi@nhs.net</t>
+          <t>yhs-tr.foirequests@nhs.net</t>
         </is>
       </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.wchc.nhs.uk/about/freedom-information/act/</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>no listed emails on either page; phone-only contact; Wirral Community: contact page lists media phone numbers but no email; FOI page lists no email; sub-paths 404. 2026-08-15: press address re-confirmed unchanged; press_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/corporate-services/communications-marketing/]. 2026-08-15: foi address re-confirmed unchanged; foi_source_url repointed from the May 2026 spreadsheet placeholder to the live page [https://www.wchc.nhs.uk/about/freedom-information/act/].</t>
-        </is>
-      </c>
+          <t>https://www.yorkhospitals.nhs.uk/about-us/information-governance/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Wirral University Teaching Hospital NHS Foundation Trust</t>
+          <t>Yorkshire Ambulance Service NHS Trust</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RBL</t>
+          <t>RX8</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>wih-tr.communications@nhs.net</t>
+          <t>yas.pressoffice@nhs.net</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://www.wuth.nhs.uk/contact-us</t>
+          <t>https://www.yas.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>wih-tr.accesstoinformationoffice@nhs.net</t>
+          <t>yas.foi@nhs.net</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.wuth.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>FOI inbox combined with Access to Information Office (handles both FOI and SARs)</t>
-        </is>
-      </c>
+          <t>https://www.yas.nhs.uk/contact-us/</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Worcestershire Acute Hospitals NHS Trust</t>
+          <t>North London NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RWP</t>
+          <t>G6V2S</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>wah-tr.communications@nhs.net</t>
+          <t>nlft.communications@nhs.net</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://www.worcsacute.nhs.uk/contact-us/press-office/</t>
+          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>wah-tr.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr"/>
+          <t>nlft.freedom.information@nhs.net</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>nlft.information.request@nhs.net</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.worcsacute.nhs.uk/our-trust/freedom-of-information/freedom-of-information-publication-scheme/</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>https://www.northlondonmentalhealth.nhs.uk/freedom-of-information</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-08-22 ODS merge reconciliation: row RNK (Tavistock and Portman) retired and folded in; Tavistock dissolved into North London NHS FT on 1 Apr 2026 and tavistockandportman.nhs.uk 301-redirects here. North London FT was formed Nov 2024 from Camden and Islington FT (TAF) and Barnet, Enfield and Haringey MH Trust (RRP). Press and FOI emails from northlondonmentalhealth.nhs.uk.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Wrightington, Wigan and Leigh Teaching Hospitals NHS Foundation Trust</t>
+          <t>The Online NHS Trust</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RRF</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>PRenquiries@wwl.nhs.uk</t>
-        </is>
-      </c>
+          <t>K0N6A</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>https://www.wwl.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>FOI@wwl.nhs.uk</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>https://www.wwl.nhs.uk/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Wye Valley NHS Trust</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>RLQ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>WVTcommsteam@wvt.nhs.uk</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>https://www.wyevalley.nhs.uk/news-events/press-office.aspx</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Freedom.Information@wvt.nhs.uk</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>https://www.wyevalley.nhs.uk/about-us/information-requests/</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>2026-08-18: press and FOI emails both re-verified against the trust's own pages. foi_source_url repointed - the old freedom-of-information-requests.aspx now 404s. Press office page also lists three named comms staff (John Burnett, comms and engagement manager; Amanda Millichip and Fiona Gurney, comms officers) on 01432 372928. | 2026-08-22: foi_source_url repointed again - make-a-freedom-of-information-request.aspx now 404s; Freedom.Information@wvt.nhs.uk is published on the parent /about-us/information-requests/ page. Press address re-confirmed on the press office page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>York and Scarborough Teaching Hospitals NHS Foundation Trust</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>RCB</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>yhs-tr.communications.team@nhs.net</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>https://www.yorkhospitals.nhs.uk/news-amp-media/media-enquiries/</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>yhs-tr.foirequests@nhs.net</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>https://www.yorkhospitals.nhs.uk/about-us/information-governance/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Yorkshire Ambulance Service NHS Trust</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>RX8</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>yas.pressoffice@nhs.net</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>https://www.yas.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>yas.foi@nhs.net</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>https://www.yas.nhs.uk/contact-us/</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>North London NHS Foundation Trust</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>G6V2S</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>nlft.communications@nhs.net</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>https://www.northlondonmentalhealth.nhs.uk/contact-us</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>nlft.freedom.information@nhs.net</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>nlft.information.request@nhs.net</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>https://www.northlondonmentalhealth.nhs.uk/freedom-of-information</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>added 2026-05-16; new entity formed Nov 2024 from merger of Camden &amp; Islington FT (TAF) and Barnet, Enfield and Haringey MH Trust (RRP); contacts to be populated by next rotation batch; press + FOI emails populated 2026-05-16 from northlondonmentalhealth.nhs.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>The Online NHS Trust</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>K0N6A</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr">
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
         <is>
           <t>Shadow / pre-legal trust as of 2026-05-16. ODS operational date 2026-04-07; legal establishment date 2026-06-01. No public website, press office or FOI process yet. Registered address is DHSC HQ (Wellington House, 133-155 Waterloo Road, London SE1 8UG). Until the trust is operational with patients (expected 2027), route press enquiries via NHS England press office (nhsengland.media@nhs.net) and FOI requests via NHS England (england.contactus@nhs.net) or DHSC.</t>
         </is>

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -2239,7 +2239,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>East and North Hertfordshire NHS Trust</t>
+          <t>East and North Hertfordshire Teaching NHS Trust</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kent and Medway NHS and Social Care Partnership Trust</t>
+          <t>Kent and Medway Mental Health NHS Trust</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5216,7 +5216,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Portsmouth Hospitals University National Health Service Trust</t>
+          <t>Portsmouth Hospitals University NHS Trust</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Royal Surrey County Hospital NHS Foundation Trust</t>
+          <t>Royal Surrey NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5762,7 +5762,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sheffield Health and Social Care NHS Foundation Trust</t>
+          <t>Sheffield Health Partnership University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>South West Yorkshire Partnership NHS Foundation Trust</t>
+          <t>South West Yorkshire Partnership Teaching NHS Foundation Trust</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7276,7 +7276,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>United Lincolnshire Hospitals NHS Trust</t>
+          <t>United Lincolnshire Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">

--- a/trust-contacts.xlsx
+++ b/trust-contacts.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>press email not found on site; FOI email not found on site; Ashford &amp; St Peter's website returns empty body / Cloudflare-blocked to WebFetch on /, /contact-us, /freedom-of-information. Could not verify any email. | press_email &amp; foi_email re-verified on site 2026-06-27 (Useful Contacts page, JS-obfuscated mailto); source_urls updated from xlsx placeholder, emails unchanged</t>
+          <t>press email not found on site; FOI email not found on site; Ashford &amp; St Peter's website returns empty body / Cloudflare-blocked to WebFetch on /, /contact-us, /freedom-of-information. Could not verify any email. | press_email &amp; foi_email re-verified on site 2026-06-27 (Useful Contacts page, JS-obfuscated mailto); source_urls updated from xlsx placeholder, emails unchanged verified 2026-09-05: both addresses unchanged. Note for future runs - ashfordstpeters.nhs.uk hides addresses in Joomla 4 &lt;joomla-hidden-mail&gt; tags (base64 in the first/last/text attributes), NOT Cloudflare cfemail, so a plain regex and decode_cfemail.py both find nothing. Base64-decode the text= attribute instead; no browser needed.</t>
         </is>
       </c>
     </row>
@@ -1867,10 +1867,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>dbth.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Adam.Tingle@nhs.net</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>https://www.dbth.nhs.uk/contact/communications-team/</t>
@@ -1893,7 +1897,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address. | press_email re-verified 2026-06-27 on Communications Team page; source_url updated from xlsx placeholder, email unchanged</t>
+          <t>FOI is named individual; Doncaster &amp; Bassetlaw publishes only personal comms emails (Emma.Shaheen@nhs.net, adam.tingle@nhs.net) - no generic press address. | press_email re-verified 2026-06-27 on Communications Team page; source_url updated from xlsx placeholder, email unchanged primary updated 2026-09-05 from https://www.dbth.nhs.uk/contact/communications-team/ (page's Media enquiries section now names the generic team mailbox dbth.comms@nhs.net); prior value Adam.Tingle@nhs.net moved to _alt.</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.gmmh.nhs.uk/contact-us</t>
+          <t>https://www.gmmh.nhs.uk/media-centre</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2710,7 +2714,11 @@
           <t>https://www.gmmh.nhs.uk/contact-us</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>source url updated 2026-09-05: press address unchanged (communications@gmmh.nhs.uk) but it is no longer printed on https://www.gmmh.nhs.uk/contact-us - it now sits on https://www.gmmh.nhs.uk/media-centre, verified there this run.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
